--- a/public/resources/BUDGET - Pros de la beauté.xlsx
+++ b/public/resources/BUDGET - Pros de la beauté.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adsgestionca.sharepoint.com/sites/AudreyJames/Shared Documents/Organisateur dépense/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adsgestionca.sharepoint.com/sites/QUIPE-AudreyDroletSamson/Documents partages/Template - fichiers maîtres/Organisateur dépense - Budget/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="499" documentId="8_{13F3CCF0-BCA8-4CC1-8B2A-DF0FF2FCD021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C861E29-5B2C-43E9-8C9F-130C847F3518}"/>
+  <xr:revisionPtr revIDLastSave="594" documentId="8_{13F3CCF0-BCA8-4CC1-8B2A-DF0FF2FCD021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0C562D4-5AF5-9443-B59D-0A4CE497EEAD}"/>
   <bookViews>
-    <workbookView xWindow="31800" yWindow="1740" windowWidth="30620" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31800" yWindow="-500" windowWidth="30620" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget - Pros de la beauté" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>coupe, brushing, coloration, mèches, permanentes, traitements capillaires</t>
         </r>
@@ -97,7 +96,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B41" authorId="0" shapeId="0" xr:uid="{C663CD77-CBC5-F846-80BE-9F858B300417}">
+    <comment ref="B46" authorId="0" shapeId="0" xr:uid="{C663CD77-CBC5-F846-80BE-9F858B300417}">
       <text>
         <r>
           <rPr>
@@ -111,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B42" authorId="0" shapeId="0" xr:uid="{5D7878DE-C2CE-5D4E-904B-44942376D7C7}">
+    <comment ref="B47" authorId="0" shapeId="0" xr:uid="{5D7878DE-C2CE-5D4E-904B-44942376D7C7}">
       <text>
         <r>
           <rPr>
@@ -125,7 +124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B43" authorId="0" shapeId="0" xr:uid="{85C03911-EC50-BD4C-9DEF-3087220DD8E8}">
+    <comment ref="B48" authorId="0" shapeId="0" xr:uid="{85C03911-EC50-BD4C-9DEF-3087220DD8E8}">
       <text>
         <r>
           <rPr>
@@ -133,13 +132,12 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>gants, serviettes, draps d’examen, cotons, etc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="0" shapeId="0" xr:uid="{6CC361E5-E374-FF46-AF79-A5A3D9ABC45F}">
+    <comment ref="B49" authorId="0" shapeId="0" xr:uid="{6CC361E5-E374-FF46-AF79-A5A3D9ABC45F}">
       <text>
         <r>
           <rPr>
@@ -173,7 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B45" authorId="0" shapeId="0" xr:uid="{14110B51-1253-1549-AC8C-C7AEF6B11E39}">
+    <comment ref="B50" authorId="0" shapeId="0" xr:uid="{14110B51-1253-1549-AC8C-C7AEF6B11E39}">
       <text>
         <r>
           <rPr>
@@ -187,7 +185,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{E88B75E7-B31F-1543-B3E4-7E5FA6F29CAB}">
+    <comment ref="B58" authorId="0" shapeId="0" xr:uid="{E88B75E7-B31F-1543-B3E4-7E5FA6F29CAB}">
       <text>
         <r>
           <rPr>
@@ -227,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
   <si>
     <t>Revenus</t>
   </si>
@@ -274,9 +272,6 @@
     <t>Services :</t>
   </si>
   <si>
-    <t xml:space="preserve">Total : </t>
-  </si>
-  <si>
     <t>Coiffure</t>
   </si>
   <si>
@@ -482,6 +477,39 @@
   </si>
   <si>
     <t>Dépenses totales</t>
+  </si>
+  <si>
+    <t>Total ventes de produits :</t>
+  </si>
+  <si>
+    <t>Total services :</t>
+  </si>
+  <si>
+    <t>Total revenus de location :</t>
+  </si>
+  <si>
+    <t>Total autres revenus :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total loyer et charges d'occupation : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total fournitures professionnelles : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total salaires et avantages : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total marketing et publicité : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total frais administratifs : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total déplacements et représentation : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total autres charges : </t>
   </si>
 </sst>
 </file>
@@ -492,7 +520,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;$&quot;"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ \ [$$-C0C]_ ;_ * \-#,##0.00\ \ [$$-C0C]_ ;_ * &quot;-&quot;??_ \ [$$-C0C]_ ;_ @_ "/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,8 +632,20 @@
       <color rgb="FF1B3C53"/>
       <name val="Aptos Display"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -640,12 +680,27 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1AE93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -655,7 +710,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -736,12 +791,6 @@
     <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -766,8 +815,21 @@
     <xf numFmtId="165" fontId="18" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -776,6 +838,63 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="38">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD2C1B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFCF8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF456882"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF456882"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF456882"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1569,72 +1688,15 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD2C1B6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFCF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF456882"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF456882"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF456882"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="6" xr9:uid="{2E3B7F73-AD13-CD40-9471-C6DD1DEB2D5F}">
-      <tableStyleElement type="wholeTable" dxfId="37"/>
-      <tableStyleElement type="headerRow" dxfId="36"/>
-      <tableStyleElement type="totalRow" dxfId="35"/>
-      <tableStyleElement type="lastColumn" dxfId="34"/>
-      <tableStyleElement type="firstRowStripe" dxfId="33"/>
-      <tableStyleElement type="secondRowStripe" dxfId="32"/>
+      <tableStyleElement type="wholeTable" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="totalRow" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1722,8 +1784,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13C5FA62-0D39-C146-966B-D9A3B9A0EA83}" name="income" displayName="income" ref="B2:O25" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" headerRowCellStyle="Accent5">
-  <autoFilter ref="B2:O25" xr:uid="{13C5FA62-0D39-C146-966B-D9A3B9A0EA83}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13C5FA62-0D39-C146-966B-D9A3B9A0EA83}" name="income" displayName="income" ref="B2:O29" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" headerRowCellStyle="Accent5">
+  <autoFilter ref="B2:O29" xr:uid="{13C5FA62-0D39-C146-966B-D9A3B9A0EA83}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1740,28 +1802,28 @@
     <filterColumn colId="13" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{F03A7D59-5788-C24B-BFBC-C1AE9D9D89AC}" name="Revenus" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{1F9070E3-7B29-4246-A87C-66B5A65313EC}" name="Janvier" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{C7BB212B-02DD-7B44-92C2-D58093F4207E}" name="Février" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{B06EDA59-9302-E743-9EAB-26C7B9DCA877}" name="Mars" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{4A0BDDD9-1757-8E4E-9D79-7E2C55F962BE}" name="Avril" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{4AB932B9-6ECA-6C44-A796-BF9DE635BAAC}" name="Mai" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{642429CB-0D70-8D49-8903-FD75270D3768}" name="Juin" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{4D4FF831-E07E-A541-AD50-A5717D0E0C66}" name="Juillet" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{651025FB-94FC-4E46-AF20-08F9C000ED94}" name="Août" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{2E6A2B62-C2D9-B842-BE6F-7B3BDA1E3350}" name="Sept" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{85617458-DBF8-F740-85FB-7F15E5D351AF}" name="Oct" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{99C55FFF-723A-7F46-B7A4-EFFCC360B3BC}" name="Nov" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{7C32AC05-F1CB-2D4A-87D1-623252B54C24}" name="Déc" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{023B6E2F-A1D8-0E41-90BB-2132E37D7DED}" name="Total" dataDxfId="16" dataCellStyle="Accent1"/>
+    <tableColumn id="1" xr3:uid="{F03A7D59-5788-C24B-BFBC-C1AE9D9D89AC}" name="Revenus" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{1F9070E3-7B29-4246-A87C-66B5A65313EC}" name="Janvier" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{C7BB212B-02DD-7B44-92C2-D58093F4207E}" name="Février" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{B06EDA59-9302-E743-9EAB-26C7B9DCA877}" name="Mars" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{4A0BDDD9-1757-8E4E-9D79-7E2C55F962BE}" name="Avril" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{4AB932B9-6ECA-6C44-A796-BF9DE635BAAC}" name="Mai" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{642429CB-0D70-8D49-8903-FD75270D3768}" name="Juin" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{4D4FF831-E07E-A541-AD50-A5717D0E0C66}" name="Juillet" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{651025FB-94FC-4E46-AF20-08F9C000ED94}" name="Août" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{2E6A2B62-C2D9-B842-BE6F-7B3BDA1E3350}" name="Sept" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{85617458-DBF8-F740-85FB-7F15E5D351AF}" name="Oct" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{99C55FFF-723A-7F46-B7A4-EFFCC360B3BC}" name="Nov" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{7C32AC05-F1CB-2D4A-87D1-623252B54C24}" name="Déc" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{023B6E2F-A1D8-0E41-90BB-2132E37D7DED}" name="Total" dataDxfId="22" dataCellStyle="Accent1"/>
   </tableColumns>
-  <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B66D6E5F-B806-0F42-BF93-C697A3628B74}" name="outcomes" displayName="outcomes" ref="B27:O84" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowCellStyle="Accent5">
-  <autoFilter ref="B27:O84" xr:uid="{B66D6E5F-B806-0F42-BF93-C697A3628B74}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B66D6E5F-B806-0F42-BF93-C697A3628B74}" name="outcomes" displayName="outcomes" ref="B31:O95" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Accent5">
+  <autoFilter ref="B31:O95" xr:uid="{B66D6E5F-B806-0F42-BF93-C697A3628B74}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1778,22 +1840,22 @@
     <filterColumn colId="13" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{D6780B85-0999-8C42-96BD-DE3560BADAF7}" name="Dépenses" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{135BF3CA-7140-EF4D-BF2C-4C6C7FD9E4C3}" name="Janvier" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{D20806E6-0E7E-174A-BE98-629FEE3444BD}" name="Février" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{0609CB8B-F087-9E40-BEC3-61A519BCAE63}" name="Mars" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{73D1E4D4-D736-4840-89C4-6EE15E4EF9A5}" name="Avril" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{EB67DBA3-8111-4240-8845-013F210C4A15}" name="Mai" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{C171ADB7-E8FB-124D-BAEE-554149E861D3}" name="Juin" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{3FCCB259-B407-AF44-9E86-50BA0E6F9492}" name="Juillet" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{01DD427C-1C22-424E-AE43-B9402E03A2E8}" name="Août" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{83C3DB5D-B0AA-064E-818C-4366B17C08B3}" name="Sept" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{32E3A5FB-7326-034D-9AEB-F82876FDB14C}" name="Oct" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{78E14C09-88C9-B646-A6B0-30BF0635B08F}" name="Nov" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{F32D0D76-EA9A-664D-ACD4-03AC085E285D}" name="Déc" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{41045F9D-1828-EC48-AB30-E0CF55D779E2}" name="Total" dataDxfId="0" dataCellStyle="Accent1"/>
+    <tableColumn id="1" xr3:uid="{D6780B85-0999-8C42-96BD-DE3560BADAF7}" name="Dépenses" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{135BF3CA-7140-EF4D-BF2C-4C6C7FD9E4C3}" name="Janvier" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{D20806E6-0E7E-174A-BE98-629FEE3444BD}" name="Février" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{0609CB8B-F087-9E40-BEC3-61A519BCAE63}" name="Mars" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{73D1E4D4-D736-4840-89C4-6EE15E4EF9A5}" name="Avril" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{EB67DBA3-8111-4240-8845-013F210C4A15}" name="Mai" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{C171ADB7-E8FB-124D-BAEE-554149E861D3}" name="Juin" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{3FCCB259-B407-AF44-9E86-50BA0E6F9492}" name="Juillet" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{01DD427C-1C22-424E-AE43-B9402E03A2E8}" name="Août" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{83C3DB5D-B0AA-064E-818C-4366B17C08B3}" name="Sept" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{32E3A5FB-7326-034D-9AEB-F82876FDB14C}" name="Oct" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{78E14C09-88C9-B646-A6B0-30BF0635B08F}" name="Nov" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F32D0D76-EA9A-664D-ACD4-03AC085E285D}" name="Déc" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{41045F9D-1828-EC48-AB30-E0CF55D779E2}" name="Total" dataDxfId="6" dataCellStyle="Accent1"/>
   </tableColumns>
-  <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2063,25 +2125,25 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:DM90"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="B1:DM101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="2" customWidth="1"/>
-    <col min="2" max="2" width="47.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="3" customWidth="1"/>
-    <col min="5" max="10" width="11.28515625" style="3" customWidth="1"/>
-    <col min="11" max="14" width="12.28515625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="2" width="47.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" style="3" customWidth="1"/>
+    <col min="5" max="10" width="11.33203125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="12.33203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="67.349999999999994" customHeight="1">
+    <row r="1" spans="2:15" ht="67.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="2:15" s="4" customFormat="1" ht="27" customHeight="1">
+    <row r="2" spans="2:15" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2125,7 +2187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:15" s="4" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="3" spans="2:15" s="4" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="30" t="s">
         <v>14</v>
       </c>
@@ -2140,281 +2202,310 @@
       <c r="K3" s="29"/>
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="29"/>
+      <c r="O3" s="28"/>
+    </row>
+    <row r="4" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="28">
-        <f>SUM(O4:O8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="41">
+        <v>0</v>
+      </c>
+      <c r="D4" s="41">
+        <v>0</v>
+      </c>
+      <c r="E4" s="41">
+        <v>0</v>
+      </c>
+      <c r="F4" s="41">
+        <v>0</v>
+      </c>
+      <c r="G4" s="41">
+        <v>0</v>
+      </c>
+      <c r="H4" s="41">
+        <v>0</v>
+      </c>
+      <c r="I4" s="41">
+        <v>0</v>
+      </c>
+      <c r="J4" s="41">
+        <v>0</v>
+      </c>
+      <c r="K4" s="41">
+        <v>0</v>
+      </c>
+      <c r="L4" s="41">
+        <v>0</v>
+      </c>
+      <c r="M4" s="41">
+        <v>0</v>
+      </c>
+      <c r="N4" s="41">
+        <v>0</v>
+      </c>
+      <c r="O4" s="42">
+        <f t="shared" ref="O4:O5" si="0">SUM(C4:N4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="9">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9">
-        <v>0</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
-        <v>0</v>
-      </c>
-      <c r="O4" s="10">
-        <f t="shared" ref="O4:O5" si="0">SUM(C4:N4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="41">
+        <v>0</v>
+      </c>
+      <c r="D5" s="41">
+        <v>0</v>
+      </c>
+      <c r="E5" s="41">
+        <v>0</v>
+      </c>
+      <c r="F5" s="41">
+        <v>0</v>
+      </c>
+      <c r="G5" s="41">
+        <v>0</v>
+      </c>
+      <c r="H5" s="41">
+        <v>0</v>
+      </c>
+      <c r="I5" s="41">
+        <v>0</v>
+      </c>
+      <c r="J5" s="41">
+        <v>0</v>
+      </c>
+      <c r="K5" s="41">
+        <v>0</v>
+      </c>
+      <c r="L5" s="41">
+        <v>0</v>
+      </c>
+      <c r="M5" s="41">
+        <v>0</v>
+      </c>
+      <c r="N5" s="41">
+        <v>0</v>
+      </c>
+      <c r="O5" s="42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="9">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>0</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9">
-        <v>0</v>
-      </c>
-      <c r="L5" s="9">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9">
-        <v>0</v>
-      </c>
-      <c r="O5" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="41">
+        <v>0</v>
+      </c>
+      <c r="D6" s="41">
+        <v>0</v>
+      </c>
+      <c r="E6" s="41">
+        <v>0</v>
+      </c>
+      <c r="F6" s="41">
+        <v>0</v>
+      </c>
+      <c r="G6" s="41">
+        <v>0</v>
+      </c>
+      <c r="H6" s="41">
+        <v>0</v>
+      </c>
+      <c r="I6" s="41">
+        <v>0</v>
+      </c>
+      <c r="J6" s="41">
+        <v>0</v>
+      </c>
+      <c r="K6" s="41">
+        <v>0</v>
+      </c>
+      <c r="L6" s="41">
+        <v>0</v>
+      </c>
+      <c r="M6" s="41">
+        <v>0</v>
+      </c>
+      <c r="N6" s="41">
+        <v>0</v>
+      </c>
+      <c r="O6" s="42">
+        <f>SUM(C6:N6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="9">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9">
-        <v>0</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9">
-        <v>0</v>
-      </c>
-      <c r="O6" s="10">
-        <f>SUM(C6:N6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="41">
+        <v>0</v>
+      </c>
+      <c r="D7" s="41">
+        <v>0</v>
+      </c>
+      <c r="E7" s="41">
+        <v>0</v>
+      </c>
+      <c r="F7" s="41">
+        <v>0</v>
+      </c>
+      <c r="G7" s="41">
+        <v>0</v>
+      </c>
+      <c r="H7" s="41">
+        <v>0</v>
+      </c>
+      <c r="I7" s="41">
+        <v>0</v>
+      </c>
+      <c r="J7" s="41">
+        <v>0</v>
+      </c>
+      <c r="K7" s="41">
+        <v>0</v>
+      </c>
+      <c r="L7" s="41">
+        <v>0</v>
+      </c>
+      <c r="M7" s="41">
+        <v>0</v>
+      </c>
+      <c r="N7" s="41">
+        <v>0</v>
+      </c>
+      <c r="O7" s="42">
+        <f t="shared" ref="O7" si="1">SUM(C7:N7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="40"/>
+      <c r="C8" s="41">
+        <v>0</v>
+      </c>
+      <c r="D8" s="41">
+        <v>0</v>
+      </c>
+      <c r="E8" s="41">
+        <v>0</v>
+      </c>
+      <c r="F8" s="41">
+        <v>0</v>
+      </c>
+      <c r="G8" s="41">
+        <v>0</v>
+      </c>
+      <c r="H8" s="41">
+        <v>0</v>
+      </c>
+      <c r="I8" s="41">
+        <v>0</v>
+      </c>
+      <c r="J8" s="41">
+        <v>0</v>
+      </c>
+      <c r="K8" s="41">
+        <v>0</v>
+      </c>
+      <c r="L8" s="41">
+        <v>0</v>
+      </c>
+      <c r="M8" s="41">
+        <v>0</v>
+      </c>
+      <c r="N8" s="41">
+        <v>0</v>
+      </c>
+      <c r="O8" s="42">
+        <f t="shared" ref="O8" si="2">SUM(C8:N8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="44">
+        <f>SUM(C4:C8)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="44">
+        <f t="shared" ref="D9:O9" si="3">SUM(D4:D8)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="9">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0</v>
-      </c>
-      <c r="F7" s="9">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-      <c r="N7" s="9">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10">
-        <f t="shared" ref="O7" si="1">SUM(C7:N7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="32"/>
-    </row>
-    <row r="9" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B9" s="26" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="28"/>
+    </row>
+    <row r="11" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O9" s="28">
-        <f>SUM(O10:O14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
-        <v>0</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
-      <c r="O10" s="10">
-        <f>SUM(C10:N10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B11" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="C11" s="9">
         <v>0</v>
@@ -2457,9 +2548,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="12" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -2502,9 +2593,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="13" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="9">
         <v>0</v>
@@ -2547,138 +2638,172 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="32"/>
-    </row>
-    <row r="15" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B15" s="26" t="s">
+    <row r="14" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="10">
+        <f>SUM(C14:N14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <f>SUM(C15:N15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="44">
+        <f>SUM(C11:C15)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="44">
+        <f t="shared" ref="D16" si="4">SUM(D11:D15)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="44">
+        <f t="shared" ref="E16" si="5">SUM(E11:E15)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="44">
+        <f t="shared" ref="F16" si="6">SUM(F11:F15)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="44">
+        <f t="shared" ref="G16" si="7">SUM(G11:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="44">
+        <f t="shared" ref="H16" si="8">SUM(H11:H15)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="44">
+        <f t="shared" ref="I16" si="9">SUM(I11:I15)</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="44">
+        <f t="shared" ref="J16" si="10">SUM(J11:J15)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="44">
+        <f t="shared" ref="K16" si="11">SUM(K11:K15)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="44">
+        <f t="shared" ref="L16" si="12">SUM(L11:L15)</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="44">
+        <f t="shared" ref="M16" si="13">SUM(M11:M15)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="44">
+        <f t="shared" ref="N16" si="14">SUM(N11:N15)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="44">
+        <f t="shared" ref="O16" si="15">SUM(O11:O15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="28"/>
+    </row>
+    <row r="18" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O15" s="28">
-        <f>SUM(O16:O19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B16" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="9">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
-        <v>0</v>
-      </c>
-      <c r="O16" s="10">
-        <f>SUM(C16:N16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="9">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>0</v>
-      </c>
-      <c r="I17" s="9">
-        <v>0</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10">
-        <f>SUM(C17:N17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B18" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="C18" s="9">
         <v>0</v>
@@ -2721,2064 +2846,2318 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="10"/>
-    </row>
-    <row r="20" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B20" s="26" t="s">
+    <row r="19" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10">
+        <f>SUM(C19:N19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+      <c r="O20" s="10">
+        <f>SUM(C20:N20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="40"/>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10">
+        <f>SUM(C21:N21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="44">
+        <f>SUM(C18:C21)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="44">
+        <f t="shared" ref="D22:O22" si="16">SUM(D18:D21)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="44">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="28"/>
+    </row>
+    <row r="24" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O20" s="28">
-        <f>SUM(O21:O24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B21" s="8" t="s">
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10">
+        <f t="shared" ref="O24:O25" si="17">SUM(C24:N24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" s="11" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="9">
-        <v>0</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9">
-        <v>0</v>
-      </c>
-      <c r="G21" s="9">
-        <v>0</v>
-      </c>
-      <c r="H21" s="9">
-        <v>0</v>
-      </c>
-      <c r="I21" s="9">
-        <v>0</v>
-      </c>
-      <c r="J21" s="9">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-      <c r="N21" s="9">
-        <v>0</v>
-      </c>
-      <c r="O21" s="10">
-        <f t="shared" ref="O21:O22" si="2">SUM(C21:N21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B22" s="8" t="s">
+      <c r="C25" s="9">
+        <v>0</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
+      <c r="I25" s="9">
+        <v>0</v>
+      </c>
+      <c r="J25" s="9">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9">
+        <v>0</v>
+      </c>
+      <c r="L25" s="9">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" s="11" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="9">
-        <v>0</v>
-      </c>
-      <c r="D22" s="9">
-        <v>0</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0</v>
-      </c>
-      <c r="F22" s="9">
-        <v>0</v>
-      </c>
-      <c r="G22" s="9">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>0</v>
-      </c>
-      <c r="I22" s="9">
-        <v>0</v>
-      </c>
-      <c r="J22" s="9">
-        <v>0</v>
-      </c>
-      <c r="K22" s="9">
-        <v>0</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9">
-        <v>0</v>
-      </c>
-      <c r="N22" s="9">
-        <v>0</v>
-      </c>
-      <c r="O22" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B23" s="8" t="s">
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+      <c r="O26" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" s="11" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="40"/>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0</v>
+      </c>
+      <c r="J27" s="9">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9">
+        <v>0</v>
+      </c>
+      <c r="M27" s="9">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="44">
+        <f>SUM(C24:C27)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="44">
+        <f t="shared" ref="D28:O28" si="18">SUM(D24:D27)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="9">
-        <v>0</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>0</v>
-      </c>
-      <c r="I23" s="9">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0</v>
-      </c>
-      <c r="N23" s="9">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="10"/>
-    </row>
-    <row r="25" spans="2:15" s="11" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B25" s="12" t="s">
+      <c r="C29" s="13">
+        <f>SUM(C4:C8,C11:C15,C18:C21,C24:C27)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="13">
+        <f t="shared" ref="D29:N29" si="19">SUM(D4:D8,D11:D15,D18:D21,D24:D27)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="36">
+        <f>SUM(income[[#This Row],[Janvier]:[Déc]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="37"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="39"/>
+    </row>
+    <row r="31" spans="2:15" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="13">
-        <f>SUM(C4:C23)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
-        <f>SUM(D4:D23)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="13">
-        <f>SUM(E4:E23)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="13">
-        <f>SUM(F4:F23)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="13">
-        <f>SUM(G4:G23)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="13">
-        <f>SUM(H4:H23)</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="13">
-        <f>SUM(I4:I23)</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="13">
-        <f>SUM(J4:J23)</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="13">
-        <f>SUM(K4:K23)</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="13">
-        <f>SUM(L4:L23)</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="13">
-        <f>SUM(M4:M23)</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="13">
-        <f>SUM(N4:N23)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="38">
-        <f>SUM(income[[#This Row],[Janvier]:[Déc]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" s="11" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="41"/>
-    </row>
-    <row r="27" spans="2:15" s="11" customFormat="1" ht="28.35" customHeight="1">
-      <c r="B27" s="14" t="s">
+      <c r="C31" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B28" s="16" t="s">
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="21"/>
+    </row>
+    <row r="33" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O28" s="21">
-        <f>SUM(O29:O39)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B29" s="19" t="s">
+      <c r="C33" s="20">
+        <v>0</v>
+      </c>
+      <c r="D33" s="20">
+        <v>0</v>
+      </c>
+      <c r="E33" s="20">
+        <v>0</v>
+      </c>
+      <c r="F33" s="20">
+        <v>0</v>
+      </c>
+      <c r="G33" s="20">
+        <v>0</v>
+      </c>
+      <c r="H33" s="20">
+        <v>0</v>
+      </c>
+      <c r="I33" s="20">
+        <v>0</v>
+      </c>
+      <c r="J33" s="20">
+        <v>0</v>
+      </c>
+      <c r="K33" s="20">
+        <v>0</v>
+      </c>
+      <c r="L33" s="20">
+        <v>0</v>
+      </c>
+      <c r="M33" s="20">
+        <v>0</v>
+      </c>
+      <c r="N33" s="20">
+        <v>0</v>
+      </c>
+      <c r="O33" s="18">
+        <f t="shared" ref="O33:O34" si="20">SUM(C33:N33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="20">
-        <v>0</v>
-      </c>
-      <c r="D29" s="20">
-        <v>0</v>
-      </c>
-      <c r="E29" s="20">
-        <v>0</v>
-      </c>
-      <c r="F29" s="20">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20">
-        <v>0</v>
-      </c>
-      <c r="H29" s="20">
-        <v>0</v>
-      </c>
-      <c r="I29" s="20">
-        <v>0</v>
-      </c>
-      <c r="J29" s="20">
-        <v>0</v>
-      </c>
-      <c r="K29" s="20">
-        <v>0</v>
-      </c>
-      <c r="L29" s="20">
-        <v>0</v>
-      </c>
-      <c r="M29" s="20">
-        <v>0</v>
-      </c>
-      <c r="N29" s="20">
-        <v>0</v>
-      </c>
-      <c r="O29" s="18">
-        <f t="shared" ref="O29:O30" si="3">SUM(C29:N29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B30" s="19" t="s">
+      <c r="C34" s="20">
+        <v>0</v>
+      </c>
+      <c r="D34" s="20">
+        <v>0</v>
+      </c>
+      <c r="E34" s="20">
+        <v>0</v>
+      </c>
+      <c r="F34" s="20">
+        <v>0</v>
+      </c>
+      <c r="G34" s="20">
+        <v>0</v>
+      </c>
+      <c r="H34" s="20">
+        <v>0</v>
+      </c>
+      <c r="I34" s="20">
+        <v>0</v>
+      </c>
+      <c r="J34" s="20">
+        <v>0</v>
+      </c>
+      <c r="K34" s="20">
+        <v>0</v>
+      </c>
+      <c r="L34" s="20">
+        <v>0</v>
+      </c>
+      <c r="M34" s="20">
+        <v>0</v>
+      </c>
+      <c r="N34" s="20">
+        <v>0</v>
+      </c>
+      <c r="O34" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="20">
-        <v>0</v>
-      </c>
-      <c r="D30" s="20">
-        <v>0</v>
-      </c>
-      <c r="E30" s="20">
-        <v>0</v>
-      </c>
-      <c r="F30" s="20">
-        <v>0</v>
-      </c>
-      <c r="G30" s="20">
-        <v>0</v>
-      </c>
-      <c r="H30" s="20">
-        <v>0</v>
-      </c>
-      <c r="I30" s="20">
-        <v>0</v>
-      </c>
-      <c r="J30" s="20">
-        <v>0</v>
-      </c>
-      <c r="K30" s="20">
-        <v>0</v>
-      </c>
-      <c r="L30" s="20">
-        <v>0</v>
-      </c>
-      <c r="M30" s="20">
-        <v>0</v>
-      </c>
-      <c r="N30" s="20">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B31" s="19" t="s">
+      <c r="C35" s="20">
+        <v>0</v>
+      </c>
+      <c r="D35" s="20">
+        <v>0</v>
+      </c>
+      <c r="E35" s="20">
+        <v>0</v>
+      </c>
+      <c r="F35" s="20">
+        <v>0</v>
+      </c>
+      <c r="G35" s="20">
+        <v>0</v>
+      </c>
+      <c r="H35" s="20">
+        <v>0</v>
+      </c>
+      <c r="I35" s="20">
+        <v>0</v>
+      </c>
+      <c r="J35" s="20">
+        <v>0</v>
+      </c>
+      <c r="K35" s="20">
+        <v>0</v>
+      </c>
+      <c r="L35" s="20">
+        <v>0</v>
+      </c>
+      <c r="M35" s="20">
+        <v>0</v>
+      </c>
+      <c r="N35" s="20">
+        <v>0</v>
+      </c>
+      <c r="O35" s="18">
+        <f t="shared" ref="O35:O42" si="21">SUM(C35:N35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="20">
-        <v>0</v>
-      </c>
-      <c r="D31" s="20">
-        <v>0</v>
-      </c>
-      <c r="E31" s="20">
-        <v>0</v>
-      </c>
-      <c r="F31" s="20">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20">
-        <v>0</v>
-      </c>
-      <c r="H31" s="20">
-        <v>0</v>
-      </c>
-      <c r="I31" s="20">
-        <v>0</v>
-      </c>
-      <c r="J31" s="20">
-        <v>0</v>
-      </c>
-      <c r="K31" s="20">
-        <v>0</v>
-      </c>
-      <c r="L31" s="20">
-        <v>0</v>
-      </c>
-      <c r="M31" s="20">
-        <v>0</v>
-      </c>
-      <c r="N31" s="20">
-        <v>0</v>
-      </c>
-      <c r="O31" s="18">
-        <f t="shared" ref="O31:O38" si="4">SUM(C31:N31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B32" s="19" t="s">
+      <c r="C36" s="20">
+        <v>0</v>
+      </c>
+      <c r="D36" s="20">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20">
+        <v>0</v>
+      </c>
+      <c r="F36" s="20">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20">
+        <v>0</v>
+      </c>
+      <c r="H36" s="20">
+        <v>0</v>
+      </c>
+      <c r="I36" s="20">
+        <v>0</v>
+      </c>
+      <c r="J36" s="20">
+        <v>0</v>
+      </c>
+      <c r="K36" s="20">
+        <v>0</v>
+      </c>
+      <c r="L36" s="20">
+        <v>0</v>
+      </c>
+      <c r="M36" s="20">
+        <v>0</v>
+      </c>
+      <c r="N36" s="20">
+        <v>0</v>
+      </c>
+      <c r="O36" s="18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20">
-        <v>0</v>
-      </c>
-      <c r="D32" s="20">
-        <v>0</v>
-      </c>
-      <c r="E32" s="20">
-        <v>0</v>
-      </c>
-      <c r="F32" s="20">
-        <v>0</v>
-      </c>
-      <c r="G32" s="20">
-        <v>0</v>
-      </c>
-      <c r="H32" s="20">
-        <v>0</v>
-      </c>
-      <c r="I32" s="20">
-        <v>0</v>
-      </c>
-      <c r="J32" s="20">
-        <v>0</v>
-      </c>
-      <c r="K32" s="20">
-        <v>0</v>
-      </c>
-      <c r="L32" s="20">
-        <v>0</v>
-      </c>
-      <c r="M32" s="20">
-        <v>0</v>
-      </c>
-      <c r="N32" s="20">
-        <v>0</v>
-      </c>
-      <c r="O32" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B33" s="19" t="s">
+      <c r="C37" s="20">
+        <v>0</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0</v>
+      </c>
+      <c r="F37" s="20">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
+      <c r="H37" s="20">
+        <v>0</v>
+      </c>
+      <c r="I37" s="20">
+        <v>0</v>
+      </c>
+      <c r="J37" s="20">
+        <v>0</v>
+      </c>
+      <c r="K37" s="20">
+        <v>0</v>
+      </c>
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
+        <v>0</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="20">
-        <v>0</v>
-      </c>
-      <c r="D33" s="20">
-        <v>0</v>
-      </c>
-      <c r="E33" s="20">
-        <v>0</v>
-      </c>
-      <c r="F33" s="20">
-        <v>0</v>
-      </c>
-      <c r="G33" s="20">
-        <v>0</v>
-      </c>
-      <c r="H33" s="20">
-        <v>0</v>
-      </c>
-      <c r="I33" s="20">
-        <v>0</v>
-      </c>
-      <c r="J33" s="20">
-        <v>0</v>
-      </c>
-      <c r="K33" s="20">
-        <v>0</v>
-      </c>
-      <c r="L33" s="20">
-        <v>0</v>
-      </c>
-      <c r="M33" s="20">
-        <v>0</v>
-      </c>
-      <c r="N33" s="20">
-        <v>0</v>
-      </c>
-      <c r="O33" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B34" s="19" t="s">
+      <c r="C38" s="20">
+        <v>0</v>
+      </c>
+      <c r="D38" s="20">
+        <v>0</v>
+      </c>
+      <c r="E38" s="20">
+        <v>0</v>
+      </c>
+      <c r="F38" s="20">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20">
+        <v>0</v>
+      </c>
+      <c r="H38" s="20">
+        <v>0</v>
+      </c>
+      <c r="I38" s="20">
+        <v>0</v>
+      </c>
+      <c r="J38" s="20">
+        <v>0</v>
+      </c>
+      <c r="K38" s="20">
+        <v>0</v>
+      </c>
+      <c r="L38" s="20">
+        <v>0</v>
+      </c>
+      <c r="M38" s="20">
+        <v>0</v>
+      </c>
+      <c r="N38" s="20">
+        <v>0</v>
+      </c>
+      <c r="O38" s="18">
+        <f t="shared" ref="O38" si="22">SUM(C38:N38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="20">
-        <v>0</v>
-      </c>
-      <c r="D34" s="20">
-        <v>0</v>
-      </c>
-      <c r="E34" s="20">
-        <v>0</v>
-      </c>
-      <c r="F34" s="20">
-        <v>0</v>
-      </c>
-      <c r="G34" s="20">
-        <v>0</v>
-      </c>
-      <c r="H34" s="20">
-        <v>0</v>
-      </c>
-      <c r="I34" s="20">
-        <v>0</v>
-      </c>
-      <c r="J34" s="20">
-        <v>0</v>
-      </c>
-      <c r="K34" s="20">
-        <v>0</v>
-      </c>
-      <c r="L34" s="20">
-        <v>0</v>
-      </c>
-      <c r="M34" s="20">
-        <v>0</v>
-      </c>
-      <c r="N34" s="20">
-        <v>0</v>
-      </c>
-      <c r="O34" s="18">
-        <f t="shared" ref="O34" si="5">SUM(C34:N34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B35" s="19" t="s">
+      <c r="C39" s="20">
+        <v>0</v>
+      </c>
+      <c r="D39" s="20">
+        <v>0</v>
+      </c>
+      <c r="E39" s="20">
+        <v>0</v>
+      </c>
+      <c r="F39" s="20">
+        <v>0</v>
+      </c>
+      <c r="G39" s="20">
+        <v>0</v>
+      </c>
+      <c r="H39" s="20">
+        <v>0</v>
+      </c>
+      <c r="I39" s="20">
+        <v>0</v>
+      </c>
+      <c r="J39" s="20">
+        <v>0</v>
+      </c>
+      <c r="K39" s="20">
+        <v>0</v>
+      </c>
+      <c r="L39" s="20">
+        <v>0</v>
+      </c>
+      <c r="M39" s="20">
+        <v>0</v>
+      </c>
+      <c r="N39" s="20">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="20">
-        <v>0</v>
-      </c>
-      <c r="D35" s="20">
-        <v>0</v>
-      </c>
-      <c r="E35" s="20">
-        <v>0</v>
-      </c>
-      <c r="F35" s="20">
-        <v>0</v>
-      </c>
-      <c r="G35" s="20">
-        <v>0</v>
-      </c>
-      <c r="H35" s="20">
-        <v>0</v>
-      </c>
-      <c r="I35" s="20">
-        <v>0</v>
-      </c>
-      <c r="J35" s="20">
-        <v>0</v>
-      </c>
-      <c r="K35" s="20">
-        <v>0</v>
-      </c>
-      <c r="L35" s="20">
-        <v>0</v>
-      </c>
-      <c r="M35" s="20">
-        <v>0</v>
-      </c>
-      <c r="N35" s="20">
-        <v>0</v>
-      </c>
-      <c r="O35" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B36" s="19" t="s">
+      <c r="C40" s="20">
+        <v>0</v>
+      </c>
+      <c r="D40" s="20">
+        <v>0</v>
+      </c>
+      <c r="E40" s="20">
+        <v>0</v>
+      </c>
+      <c r="F40" s="20">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20">
+        <v>0</v>
+      </c>
+      <c r="H40" s="20">
+        <v>0</v>
+      </c>
+      <c r="I40" s="20">
+        <v>0</v>
+      </c>
+      <c r="J40" s="20">
+        <v>0</v>
+      </c>
+      <c r="K40" s="20">
+        <v>0</v>
+      </c>
+      <c r="L40" s="20">
+        <v>0</v>
+      </c>
+      <c r="M40" s="20">
+        <v>0</v>
+      </c>
+      <c r="N40" s="20">
+        <v>0</v>
+      </c>
+      <c r="O40" s="18">
+        <f t="shared" ref="O40:O41" si="23">SUM(C40:N40)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="20">
-        <v>0</v>
-      </c>
-      <c r="D36" s="20">
-        <v>0</v>
-      </c>
-      <c r="E36" s="20">
-        <v>0</v>
-      </c>
-      <c r="F36" s="20">
-        <v>0</v>
-      </c>
-      <c r="G36" s="20">
-        <v>0</v>
-      </c>
-      <c r="H36" s="20">
-        <v>0</v>
-      </c>
-      <c r="I36" s="20">
-        <v>0</v>
-      </c>
-      <c r="J36" s="20">
-        <v>0</v>
-      </c>
-      <c r="K36" s="20">
-        <v>0</v>
-      </c>
-      <c r="L36" s="20">
-        <v>0</v>
-      </c>
-      <c r="M36" s="20">
-        <v>0</v>
-      </c>
-      <c r="N36" s="20">
-        <v>0</v>
-      </c>
-      <c r="O36" s="18">
-        <f t="shared" ref="O36:O37" si="6">SUM(C36:N36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B37" s="19" t="s">
+      <c r="C41" s="20">
+        <v>0</v>
+      </c>
+      <c r="D41" s="20">
+        <v>0</v>
+      </c>
+      <c r="E41" s="20">
+        <v>0</v>
+      </c>
+      <c r="F41" s="20">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20">
+        <v>0</v>
+      </c>
+      <c r="H41" s="20">
+        <v>0</v>
+      </c>
+      <c r="I41" s="20">
+        <v>0</v>
+      </c>
+      <c r="J41" s="20">
+        <v>0</v>
+      </c>
+      <c r="K41" s="20">
+        <v>0</v>
+      </c>
+      <c r="L41" s="20">
+        <v>0</v>
+      </c>
+      <c r="M41" s="20">
+        <v>0</v>
+      </c>
+      <c r="N41" s="20">
+        <v>0</v>
+      </c>
+      <c r="O41" s="18">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="20">
-        <v>0</v>
-      </c>
-      <c r="D37" s="20">
-        <v>0</v>
-      </c>
-      <c r="E37" s="20">
-        <v>0</v>
-      </c>
-      <c r="F37" s="20">
-        <v>0</v>
-      </c>
-      <c r="G37" s="20">
-        <v>0</v>
-      </c>
-      <c r="H37" s="20">
-        <v>0</v>
-      </c>
-      <c r="I37" s="20">
-        <v>0</v>
-      </c>
-      <c r="J37" s="20">
-        <v>0</v>
-      </c>
-      <c r="K37" s="20">
-        <v>0</v>
-      </c>
-      <c r="L37" s="20">
-        <v>0</v>
-      </c>
-      <c r="M37" s="20">
-        <v>0</v>
-      </c>
-      <c r="N37" s="20">
-        <v>0</v>
-      </c>
-      <c r="O37" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B38" s="19" t="s">
+      <c r="C42" s="20">
+        <v>0</v>
+      </c>
+      <c r="D42" s="20">
+        <v>0</v>
+      </c>
+      <c r="E42" s="20">
+        <v>0</v>
+      </c>
+      <c r="F42" s="20">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20">
+        <v>0</v>
+      </c>
+      <c r="H42" s="20">
+        <v>0</v>
+      </c>
+      <c r="I42" s="20">
+        <v>0</v>
+      </c>
+      <c r="J42" s="20">
+        <v>0</v>
+      </c>
+      <c r="K42" s="20">
+        <v>0</v>
+      </c>
+      <c r="L42" s="20">
+        <v>0</v>
+      </c>
+      <c r="M42" s="20">
+        <v>0</v>
+      </c>
+      <c r="N42" s="20">
+        <v>0</v>
+      </c>
+      <c r="O42" s="18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="45"/>
+      <c r="C43" s="20">
+        <v>0</v>
+      </c>
+      <c r="D43" s="20">
+        <v>0</v>
+      </c>
+      <c r="E43" s="20">
+        <v>0</v>
+      </c>
+      <c r="F43" s="20">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20">
+        <v>0</v>
+      </c>
+      <c r="H43" s="20">
+        <v>0</v>
+      </c>
+      <c r="I43" s="20">
+        <v>0</v>
+      </c>
+      <c r="J43" s="20">
+        <v>0</v>
+      </c>
+      <c r="K43" s="20">
+        <v>0</v>
+      </c>
+      <c r="L43" s="20">
+        <v>0</v>
+      </c>
+      <c r="M43" s="20">
+        <v>0</v>
+      </c>
+      <c r="N43" s="20">
+        <v>0</v>
+      </c>
+      <c r="O43" s="18">
+        <f t="shared" ref="O43" si="24">SUM(C43:N43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="44">
+        <f>SUM(C33:C43)</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="44">
+        <f t="shared" ref="D44:O44" si="25">SUM(D33:D43)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="20">
-        <v>0</v>
-      </c>
-      <c r="D38" s="20">
-        <v>0</v>
-      </c>
-      <c r="E38" s="20">
-        <v>0</v>
-      </c>
-      <c r="F38" s="20">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20">
-        <v>0</v>
-      </c>
-      <c r="H38" s="20">
-        <v>0</v>
-      </c>
-      <c r="I38" s="20">
-        <v>0</v>
-      </c>
-      <c r="J38" s="20">
-        <v>0</v>
-      </c>
-      <c r="K38" s="20">
-        <v>0</v>
-      </c>
-      <c r="L38" s="20">
-        <v>0</v>
-      </c>
-      <c r="M38" s="20">
-        <v>0</v>
-      </c>
-      <c r="N38" s="20">
-        <v>0</v>
-      </c>
-      <c r="O38" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B39" s="19"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
-      <c r="K39" s="42"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="42"/>
-      <c r="N39" s="42"/>
-      <c r="O39" s="33"/>
-    </row>
-    <row r="40" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B40" s="16" t="s">
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O40" s="21">
-        <f>SUM(O41:O47)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B41" s="19" t="s">
+      <c r="C46" s="20">
+        <v>0</v>
+      </c>
+      <c r="D46" s="20">
+        <v>0</v>
+      </c>
+      <c r="E46" s="20">
+        <v>0</v>
+      </c>
+      <c r="F46" s="20">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20">
+        <v>0</v>
+      </c>
+      <c r="H46" s="20">
+        <v>0</v>
+      </c>
+      <c r="I46" s="20">
+        <v>0</v>
+      </c>
+      <c r="J46" s="20">
+        <v>0</v>
+      </c>
+      <c r="K46" s="20">
+        <v>0</v>
+      </c>
+      <c r="L46" s="20">
+        <v>0</v>
+      </c>
+      <c r="M46" s="20">
+        <v>0</v>
+      </c>
+      <c r="N46" s="20">
+        <v>0</v>
+      </c>
+      <c r="O46" s="18">
+        <f t="shared" ref="O46:O58" si="26">SUM(C46:N46)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="20">
-        <v>0</v>
-      </c>
-      <c r="D41" s="20">
-        <v>0</v>
-      </c>
-      <c r="E41" s="20">
-        <v>0</v>
-      </c>
-      <c r="F41" s="20">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20">
-        <v>0</v>
-      </c>
-      <c r="H41" s="20">
-        <v>0</v>
-      </c>
-      <c r="I41" s="20">
-        <v>0</v>
-      </c>
-      <c r="J41" s="20">
-        <v>0</v>
-      </c>
-      <c r="K41" s="20">
-        <v>0</v>
-      </c>
-      <c r="L41" s="20">
-        <v>0</v>
-      </c>
-      <c r="M41" s="20">
-        <v>0</v>
-      </c>
-      <c r="N41" s="20">
-        <v>0</v>
-      </c>
-      <c r="O41" s="18">
-        <f t="shared" ref="O41:O52" si="7">SUM(C41:N41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B42" s="19" t="s">
+      <c r="C47" s="20">
+        <v>0</v>
+      </c>
+      <c r="D47" s="20">
+        <v>0</v>
+      </c>
+      <c r="E47" s="20">
+        <v>0</v>
+      </c>
+      <c r="F47" s="20">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20">
+        <v>0</v>
+      </c>
+      <c r="H47" s="20">
+        <v>0</v>
+      </c>
+      <c r="I47" s="20">
+        <v>0</v>
+      </c>
+      <c r="J47" s="20">
+        <v>0</v>
+      </c>
+      <c r="K47" s="20">
+        <v>0</v>
+      </c>
+      <c r="L47" s="20">
+        <v>0</v>
+      </c>
+      <c r="M47" s="20">
+        <v>0</v>
+      </c>
+      <c r="N47" s="20">
+        <v>0</v>
+      </c>
+      <c r="O47" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="20">
-        <v>0</v>
-      </c>
-      <c r="D42" s="20">
-        <v>0</v>
-      </c>
-      <c r="E42" s="20">
-        <v>0</v>
-      </c>
-      <c r="F42" s="20">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20">
-        <v>0</v>
-      </c>
-      <c r="H42" s="20">
-        <v>0</v>
-      </c>
-      <c r="I42" s="20">
-        <v>0</v>
-      </c>
-      <c r="J42" s="20">
-        <v>0</v>
-      </c>
-      <c r="K42" s="20">
-        <v>0</v>
-      </c>
-      <c r="L42" s="20">
-        <v>0</v>
-      </c>
-      <c r="M42" s="20">
-        <v>0</v>
-      </c>
-      <c r="N42" s="20">
-        <v>0</v>
-      </c>
-      <c r="O42" s="18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B43" s="19" t="s">
+      <c r="C48" s="20">
+        <v>0</v>
+      </c>
+      <c r="D48" s="20">
+        <v>0</v>
+      </c>
+      <c r="E48" s="20">
+        <v>0</v>
+      </c>
+      <c r="F48" s="20">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20">
+        <v>0</v>
+      </c>
+      <c r="H48" s="20">
+        <v>0</v>
+      </c>
+      <c r="I48" s="20">
+        <v>0</v>
+      </c>
+      <c r="J48" s="20">
+        <v>0</v>
+      </c>
+      <c r="K48" s="20">
+        <v>0</v>
+      </c>
+      <c r="L48" s="20">
+        <v>0</v>
+      </c>
+      <c r="M48" s="20">
+        <v>0</v>
+      </c>
+      <c r="N48" s="20">
+        <v>0</v>
+      </c>
+      <c r="O48" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="20">
-        <v>0</v>
-      </c>
-      <c r="D43" s="20">
-        <v>0</v>
-      </c>
-      <c r="E43" s="20">
-        <v>0</v>
-      </c>
-      <c r="F43" s="20">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20">
-        <v>0</v>
-      </c>
-      <c r="H43" s="20">
-        <v>0</v>
-      </c>
-      <c r="I43" s="20">
-        <v>0</v>
-      </c>
-      <c r="J43" s="20">
-        <v>0</v>
-      </c>
-      <c r="K43" s="20">
-        <v>0</v>
-      </c>
-      <c r="L43" s="20">
-        <v>0</v>
-      </c>
-      <c r="M43" s="20">
-        <v>0</v>
-      </c>
-      <c r="N43" s="20">
-        <v>0</v>
-      </c>
-      <c r="O43" s="18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B44" s="19" t="s">
+      <c r="C49" s="20">
+        <v>0</v>
+      </c>
+      <c r="D49" s="20">
+        <v>0</v>
+      </c>
+      <c r="E49" s="20">
+        <v>0</v>
+      </c>
+      <c r="F49" s="20">
+        <v>0</v>
+      </c>
+      <c r="G49" s="20">
+        <v>0</v>
+      </c>
+      <c r="H49" s="20">
+        <v>0</v>
+      </c>
+      <c r="I49" s="20">
+        <v>0</v>
+      </c>
+      <c r="J49" s="20">
+        <v>0</v>
+      </c>
+      <c r="K49" s="20">
+        <v>0</v>
+      </c>
+      <c r="L49" s="20">
+        <v>0</v>
+      </c>
+      <c r="M49" s="20">
+        <v>0</v>
+      </c>
+      <c r="N49" s="20">
+        <v>0</v>
+      </c>
+      <c r="O49" s="18">
+        <f t="shared" ref="O49:O51" si="27">SUM(C49:N49)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="20">
-        <v>0</v>
-      </c>
-      <c r="D44" s="20">
-        <v>0</v>
-      </c>
-      <c r="E44" s="20">
-        <v>0</v>
-      </c>
-      <c r="F44" s="20">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20">
-        <v>0</v>
-      </c>
-      <c r="H44" s="20">
-        <v>0</v>
-      </c>
-      <c r="I44" s="20">
-        <v>0</v>
-      </c>
-      <c r="J44" s="20">
-        <v>0</v>
-      </c>
-      <c r="K44" s="20">
-        <v>0</v>
-      </c>
-      <c r="L44" s="20">
-        <v>0</v>
-      </c>
-      <c r="M44" s="20">
-        <v>0</v>
-      </c>
-      <c r="N44" s="20">
-        <v>0</v>
-      </c>
-      <c r="O44" s="18">
-        <f t="shared" ref="O44:O46" si="8">SUM(C44:N44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B45" t="s">
+      <c r="C50" s="20">
+        <v>0</v>
+      </c>
+      <c r="D50" s="20">
+        <v>0</v>
+      </c>
+      <c r="E50" s="20">
+        <v>0</v>
+      </c>
+      <c r="F50" s="20">
+        <v>0</v>
+      </c>
+      <c r="G50" s="20">
+        <v>0</v>
+      </c>
+      <c r="H50" s="20">
+        <v>0</v>
+      </c>
+      <c r="I50" s="20">
+        <v>0</v>
+      </c>
+      <c r="J50" s="20">
+        <v>0</v>
+      </c>
+      <c r="K50" s="20">
+        <v>0</v>
+      </c>
+      <c r="L50" s="20">
+        <v>0</v>
+      </c>
+      <c r="M50" s="20">
+        <v>0</v>
+      </c>
+      <c r="N50" s="20">
+        <v>0</v>
+      </c>
+      <c r="O50" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="20">
-        <v>0</v>
-      </c>
-      <c r="D45" s="20">
-        <v>0</v>
-      </c>
-      <c r="E45" s="20">
-        <v>0</v>
-      </c>
-      <c r="F45" s="20">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20">
-        <v>0</v>
-      </c>
-      <c r="H45" s="20">
-        <v>0</v>
-      </c>
-      <c r="I45" s="20">
-        <v>0</v>
-      </c>
-      <c r="J45" s="20">
-        <v>0</v>
-      </c>
-      <c r="K45" s="20">
-        <v>0</v>
-      </c>
-      <c r="L45" s="20">
-        <v>0</v>
-      </c>
-      <c r="M45" s="20">
-        <v>0</v>
-      </c>
-      <c r="N45" s="20">
-        <v>0</v>
-      </c>
-      <c r="O45" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B46" s="19" t="s">
+      <c r="C51" s="20">
+        <v>0</v>
+      </c>
+      <c r="D51" s="20">
+        <v>0</v>
+      </c>
+      <c r="E51" s="20">
+        <v>0</v>
+      </c>
+      <c r="F51" s="20">
+        <v>0</v>
+      </c>
+      <c r="G51" s="20">
+        <v>0</v>
+      </c>
+      <c r="H51" s="20">
+        <v>0</v>
+      </c>
+      <c r="I51" s="20">
+        <v>0</v>
+      </c>
+      <c r="J51" s="20">
+        <v>0</v>
+      </c>
+      <c r="K51" s="20">
+        <v>0</v>
+      </c>
+      <c r="L51" s="20">
+        <v>0</v>
+      </c>
+      <c r="M51" s="20">
+        <v>0</v>
+      </c>
+      <c r="N51" s="20">
+        <v>0</v>
+      </c>
+      <c r="O51" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="45"/>
+      <c r="C52" s="20">
+        <v>0</v>
+      </c>
+      <c r="D52" s="20">
+        <v>0</v>
+      </c>
+      <c r="E52" s="20">
+        <v>0</v>
+      </c>
+      <c r="F52" s="20">
+        <v>0</v>
+      </c>
+      <c r="G52" s="20">
+        <v>0</v>
+      </c>
+      <c r="H52" s="20">
+        <v>0</v>
+      </c>
+      <c r="I52" s="20">
+        <v>0</v>
+      </c>
+      <c r="J52" s="20">
+        <v>0</v>
+      </c>
+      <c r="K52" s="20">
+        <v>0</v>
+      </c>
+      <c r="L52" s="20">
+        <v>0</v>
+      </c>
+      <c r="M52" s="20">
+        <v>0</v>
+      </c>
+      <c r="N52" s="20">
+        <v>0</v>
+      </c>
+      <c r="O52" s="18">
+        <f t="shared" ref="O52" si="28">SUM(C52:N52)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" s="44">
+        <f>SUM(C46:C52)</f>
+        <v>0</v>
+      </c>
+      <c r="D53" s="44">
+        <f t="shared" ref="D53:N53" si="29">SUM(D46:D52)</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="M53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="N53" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="O53" s="44">
+        <f>SUM(O46:O52)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="20">
-        <v>0</v>
-      </c>
-      <c r="D46" s="20">
-        <v>0</v>
-      </c>
-      <c r="E46" s="20">
-        <v>0</v>
-      </c>
-      <c r="F46" s="20">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20">
-        <v>0</v>
-      </c>
-      <c r="H46" s="20">
-        <v>0</v>
-      </c>
-      <c r="I46" s="20">
-        <v>0</v>
-      </c>
-      <c r="J46" s="20">
-        <v>0</v>
-      </c>
-      <c r="K46" s="20">
-        <v>0</v>
-      </c>
-      <c r="L46" s="20">
-        <v>0</v>
-      </c>
-      <c r="M46" s="20">
-        <v>0</v>
-      </c>
-      <c r="N46" s="20">
-        <v>0</v>
-      </c>
-      <c r="O46" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B47" s="19"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="18"/>
-    </row>
-    <row r="48" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B48" s="16" t="s">
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="22"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="21"/>
+    </row>
+    <row r="55" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O48" s="21">
-        <f>SUM(O49:O54)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B49" s="19" t="s">
+      <c r="C55" s="20">
+        <v>0</v>
+      </c>
+      <c r="D55" s="20">
+        <v>0</v>
+      </c>
+      <c r="E55" s="20">
+        <v>0</v>
+      </c>
+      <c r="F55" s="20">
+        <v>0</v>
+      </c>
+      <c r="G55" s="20">
+        <v>0</v>
+      </c>
+      <c r="H55" s="20">
+        <v>0</v>
+      </c>
+      <c r="I55" s="20">
+        <v>0</v>
+      </c>
+      <c r="J55" s="20">
+        <v>0</v>
+      </c>
+      <c r="K55" s="20">
+        <v>0</v>
+      </c>
+      <c r="L55" s="20">
+        <v>0</v>
+      </c>
+      <c r="M55" s="20">
+        <v>0</v>
+      </c>
+      <c r="N55" s="20">
+        <v>0</v>
+      </c>
+      <c r="O55" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="20">
-        <v>0</v>
-      </c>
-      <c r="D49" s="20">
-        <v>0</v>
-      </c>
-      <c r="E49" s="20">
-        <v>0</v>
-      </c>
-      <c r="F49" s="20">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20">
-        <v>0</v>
-      </c>
-      <c r="H49" s="20">
-        <v>0</v>
-      </c>
-      <c r="I49" s="20">
-        <v>0</v>
-      </c>
-      <c r="J49" s="20">
-        <v>0</v>
-      </c>
-      <c r="K49" s="20">
-        <v>0</v>
-      </c>
-      <c r="L49" s="20">
-        <v>0</v>
-      </c>
-      <c r="M49" s="20">
-        <v>0</v>
-      </c>
-      <c r="N49" s="20">
-        <v>0</v>
-      </c>
-      <c r="O49" s="18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B50" s="19" t="s">
+      <c r="C56" s="20">
+        <v>0</v>
+      </c>
+      <c r="D56" s="20">
+        <v>0</v>
+      </c>
+      <c r="E56" s="20">
+        <v>0</v>
+      </c>
+      <c r="F56" s="20">
+        <v>0</v>
+      </c>
+      <c r="G56" s="20">
+        <v>0</v>
+      </c>
+      <c r="H56" s="20">
+        <v>0</v>
+      </c>
+      <c r="I56" s="20">
+        <v>0</v>
+      </c>
+      <c r="J56" s="20">
+        <v>0</v>
+      </c>
+      <c r="K56" s="20">
+        <v>0</v>
+      </c>
+      <c r="L56" s="20">
+        <v>0</v>
+      </c>
+      <c r="M56" s="20">
+        <v>0</v>
+      </c>
+      <c r="N56" s="20">
+        <v>0</v>
+      </c>
+      <c r="O56" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="20">
-        <v>0</v>
-      </c>
-      <c r="D50" s="20">
-        <v>0</v>
-      </c>
-      <c r="E50" s="20">
-        <v>0</v>
-      </c>
-      <c r="F50" s="20">
-        <v>0</v>
-      </c>
-      <c r="G50" s="20">
-        <v>0</v>
-      </c>
-      <c r="H50" s="20">
-        <v>0</v>
-      </c>
-      <c r="I50" s="20">
-        <v>0</v>
-      </c>
-      <c r="J50" s="20">
-        <v>0</v>
-      </c>
-      <c r="K50" s="20">
-        <v>0</v>
-      </c>
-      <c r="L50" s="20">
-        <v>0</v>
-      </c>
-      <c r="M50" s="20">
-        <v>0</v>
-      </c>
-      <c r="N50" s="20">
-        <v>0</v>
-      </c>
-      <c r="O50" s="18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B51" s="19" t="s">
+      <c r="C57" s="20">
+        <v>0</v>
+      </c>
+      <c r="D57" s="20">
+        <v>0</v>
+      </c>
+      <c r="E57" s="20">
+        <v>0</v>
+      </c>
+      <c r="F57" s="20">
+        <v>0</v>
+      </c>
+      <c r="G57" s="20">
+        <v>0</v>
+      </c>
+      <c r="H57" s="20">
+        <v>0</v>
+      </c>
+      <c r="I57" s="20">
+        <v>0</v>
+      </c>
+      <c r="J57" s="20">
+        <v>0</v>
+      </c>
+      <c r="K57" s="20">
+        <v>0</v>
+      </c>
+      <c r="L57" s="20">
+        <v>0</v>
+      </c>
+      <c r="M57" s="20">
+        <v>0</v>
+      </c>
+      <c r="N57" s="20">
+        <v>0</v>
+      </c>
+      <c r="O57" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="20">
-        <v>0</v>
-      </c>
-      <c r="D51" s="20">
-        <v>0</v>
-      </c>
-      <c r="E51" s="20">
-        <v>0</v>
-      </c>
-      <c r="F51" s="20">
-        <v>0</v>
-      </c>
-      <c r="G51" s="20">
-        <v>0</v>
-      </c>
-      <c r="H51" s="20">
-        <v>0</v>
-      </c>
-      <c r="I51" s="20">
-        <v>0</v>
-      </c>
-      <c r="J51" s="20">
-        <v>0</v>
-      </c>
-      <c r="K51" s="20">
-        <v>0</v>
-      </c>
-      <c r="L51" s="20">
-        <v>0</v>
-      </c>
-      <c r="M51" s="20">
-        <v>0</v>
-      </c>
-      <c r="N51" s="20">
-        <v>0</v>
-      </c>
-      <c r="O51" s="18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B52" s="19" t="s">
+      <c r="C58" s="20">
+        <v>0</v>
+      </c>
+      <c r="D58" s="20">
+        <v>0</v>
+      </c>
+      <c r="E58" s="20">
+        <v>0</v>
+      </c>
+      <c r="F58" s="20">
+        <v>0</v>
+      </c>
+      <c r="G58" s="20">
+        <v>0</v>
+      </c>
+      <c r="H58" s="20">
+        <v>0</v>
+      </c>
+      <c r="I58" s="20">
+        <v>0</v>
+      </c>
+      <c r="J58" s="20">
+        <v>0</v>
+      </c>
+      <c r="K58" s="20">
+        <v>0</v>
+      </c>
+      <c r="L58" s="20">
+        <v>0</v>
+      </c>
+      <c r="M58" s="20">
+        <v>0</v>
+      </c>
+      <c r="N58" s="20">
+        <v>0</v>
+      </c>
+      <c r="O58" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="20">
-        <v>0</v>
-      </c>
-      <c r="D52" s="20">
-        <v>0</v>
-      </c>
-      <c r="E52" s="20">
-        <v>0</v>
-      </c>
-      <c r="F52" s="20">
-        <v>0</v>
-      </c>
-      <c r="G52" s="20">
-        <v>0</v>
-      </c>
-      <c r="H52" s="20">
-        <v>0</v>
-      </c>
-      <c r="I52" s="20">
-        <v>0</v>
-      </c>
-      <c r="J52" s="20">
-        <v>0</v>
-      </c>
-      <c r="K52" s="20">
-        <v>0</v>
-      </c>
-      <c r="L52" s="20">
-        <v>0</v>
-      </c>
-      <c r="M52" s="20">
-        <v>0</v>
-      </c>
-      <c r="N52" s="20">
-        <v>0</v>
-      </c>
-      <c r="O52" s="18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B53" s="19" t="s">
+      <c r="C59" s="20">
+        <v>0</v>
+      </c>
+      <c r="D59" s="20">
+        <v>0</v>
+      </c>
+      <c r="E59" s="20">
+        <v>0</v>
+      </c>
+      <c r="F59" s="20">
+        <v>0</v>
+      </c>
+      <c r="G59" s="20">
+        <v>0</v>
+      </c>
+      <c r="H59" s="20">
+        <v>0</v>
+      </c>
+      <c r="I59" s="20">
+        <v>0</v>
+      </c>
+      <c r="J59" s="20">
+        <v>0</v>
+      </c>
+      <c r="K59" s="20">
+        <v>0</v>
+      </c>
+      <c r="L59" s="20">
+        <v>0</v>
+      </c>
+      <c r="M59" s="20">
+        <v>0</v>
+      </c>
+      <c r="N59" s="20">
+        <v>0</v>
+      </c>
+      <c r="O59" s="18">
+        <f t="shared" ref="O59" si="30">SUM(C59:N59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="45"/>
+      <c r="C60" s="20">
+        <v>0</v>
+      </c>
+      <c r="D60" s="20">
+        <v>0</v>
+      </c>
+      <c r="E60" s="20">
+        <v>0</v>
+      </c>
+      <c r="F60" s="20">
+        <v>0</v>
+      </c>
+      <c r="G60" s="20">
+        <v>0</v>
+      </c>
+      <c r="H60" s="20">
+        <v>0</v>
+      </c>
+      <c r="I60" s="20">
+        <v>0</v>
+      </c>
+      <c r="J60" s="20">
+        <v>0</v>
+      </c>
+      <c r="K60" s="20">
+        <v>0</v>
+      </c>
+      <c r="L60" s="20">
+        <v>0</v>
+      </c>
+      <c r="M60" s="20">
+        <v>0</v>
+      </c>
+      <c r="N60" s="20">
+        <v>0</v>
+      </c>
+      <c r="O60" s="18">
+        <f t="shared" ref="O60" si="31">SUM(C60:N60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="44">
+        <f>SUM(C55:C60)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="44">
+        <f t="shared" ref="D61:O61" si="32">SUM(D55:D60)</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="G61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="N61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O61" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="20">
-        <v>0</v>
-      </c>
-      <c r="D53" s="20">
-        <v>0</v>
-      </c>
-      <c r="E53" s="20">
-        <v>0</v>
-      </c>
-      <c r="F53" s="20">
-        <v>0</v>
-      </c>
-      <c r="G53" s="20">
-        <v>0</v>
-      </c>
-      <c r="H53" s="20">
-        <v>0</v>
-      </c>
-      <c r="I53" s="20">
-        <v>0</v>
-      </c>
-      <c r="J53" s="20">
-        <v>0</v>
-      </c>
-      <c r="K53" s="20">
-        <v>0</v>
-      </c>
-      <c r="L53" s="20">
-        <v>0</v>
-      </c>
-      <c r="M53" s="20">
-        <v>0</v>
-      </c>
-      <c r="N53" s="20">
-        <v>0</v>
-      </c>
-      <c r="O53" s="18">
-        <f t="shared" ref="O53" si="9">SUM(C53:N53)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B54" s="19"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="18"/>
-    </row>
-    <row r="55" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B55" s="16" t="s">
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="23"/>
+      <c r="I62" s="23"/>
+      <c r="J62" s="23"/>
+      <c r="K62" s="23"/>
+      <c r="L62" s="23"/>
+      <c r="M62" s="23"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="21"/>
+    </row>
+    <row r="63" spans="2:15" s="35" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="23"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="23"/>
-      <c r="M55" s="23"/>
-      <c r="N55" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O55" s="21">
-        <f>SUM(O56:O62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B56" s="19" t="s">
+      <c r="C63" s="20">
+        <v>0</v>
+      </c>
+      <c r="D63" s="20">
+        <v>0</v>
+      </c>
+      <c r="E63" s="20">
+        <v>0</v>
+      </c>
+      <c r="F63" s="20">
+        <v>0</v>
+      </c>
+      <c r="G63" s="20">
+        <v>0</v>
+      </c>
+      <c r="H63" s="20">
+        <v>0</v>
+      </c>
+      <c r="I63" s="20">
+        <v>0</v>
+      </c>
+      <c r="J63" s="20">
+        <v>0</v>
+      </c>
+      <c r="K63" s="20">
+        <v>0</v>
+      </c>
+      <c r="L63" s="20">
+        <v>0</v>
+      </c>
+      <c r="M63" s="20">
+        <v>0</v>
+      </c>
+      <c r="N63" s="20">
+        <v>0</v>
+      </c>
+      <c r="O63" s="18">
+        <f t="shared" ref="O63:O74" si="33">SUM(C63:N63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C56" s="20">
-        <v>0</v>
-      </c>
-      <c r="D56" s="20">
-        <v>0</v>
-      </c>
-      <c r="E56" s="20">
-        <v>0</v>
-      </c>
-      <c r="F56" s="20">
-        <v>0</v>
-      </c>
-      <c r="G56" s="20">
-        <v>0</v>
-      </c>
-      <c r="H56" s="20">
-        <v>0</v>
-      </c>
-      <c r="I56" s="20">
-        <v>0</v>
-      </c>
-      <c r="J56" s="20">
-        <v>0</v>
-      </c>
-      <c r="K56" s="20">
-        <v>0</v>
-      </c>
-      <c r="L56" s="20">
-        <v>0</v>
-      </c>
-      <c r="M56" s="20">
-        <v>0</v>
-      </c>
-      <c r="N56" s="20">
-        <v>0</v>
-      </c>
-      <c r="O56" s="18">
-        <f t="shared" ref="O56:O66" si="10">SUM(C56:N56)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B57" s="19" t="s">
+      <c r="C64" s="20">
+        <v>0</v>
+      </c>
+      <c r="D64" s="20">
+        <v>0</v>
+      </c>
+      <c r="E64" s="20">
+        <v>0</v>
+      </c>
+      <c r="F64" s="20">
+        <v>0</v>
+      </c>
+      <c r="G64" s="20">
+        <v>0</v>
+      </c>
+      <c r="H64" s="20">
+        <v>0</v>
+      </c>
+      <c r="I64" s="20">
+        <v>0</v>
+      </c>
+      <c r="J64" s="20">
+        <v>0</v>
+      </c>
+      <c r="K64" s="20">
+        <v>0</v>
+      </c>
+      <c r="L64" s="20">
+        <v>0</v>
+      </c>
+      <c r="M64" s="20">
+        <v>0</v>
+      </c>
+      <c r="N64" s="20">
+        <v>0</v>
+      </c>
+      <c r="O64" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C57" s="20">
-        <v>0</v>
-      </c>
-      <c r="D57" s="20">
-        <v>0</v>
-      </c>
-      <c r="E57" s="20">
-        <v>0</v>
-      </c>
-      <c r="F57" s="20">
-        <v>0</v>
-      </c>
-      <c r="G57" s="20">
-        <v>0</v>
-      </c>
-      <c r="H57" s="20">
-        <v>0</v>
-      </c>
-      <c r="I57" s="20">
-        <v>0</v>
-      </c>
-      <c r="J57" s="20">
-        <v>0</v>
-      </c>
-      <c r="K57" s="20">
-        <v>0</v>
-      </c>
-      <c r="L57" s="20">
-        <v>0</v>
-      </c>
-      <c r="M57" s="20">
-        <v>0</v>
-      </c>
-      <c r="N57" s="20">
-        <v>0</v>
-      </c>
-      <c r="O57" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B58" s="19" t="s">
+      <c r="C65" s="20">
+        <v>0</v>
+      </c>
+      <c r="D65" s="20">
+        <v>0</v>
+      </c>
+      <c r="E65" s="20">
+        <v>0</v>
+      </c>
+      <c r="F65" s="20">
+        <v>0</v>
+      </c>
+      <c r="G65" s="20">
+        <v>0</v>
+      </c>
+      <c r="H65" s="20">
+        <v>0</v>
+      </c>
+      <c r="I65" s="20">
+        <v>0</v>
+      </c>
+      <c r="J65" s="20">
+        <v>0</v>
+      </c>
+      <c r="K65" s="20">
+        <v>0</v>
+      </c>
+      <c r="L65" s="20">
+        <v>0</v>
+      </c>
+      <c r="M65" s="20">
+        <v>0</v>
+      </c>
+      <c r="N65" s="20">
+        <v>0</v>
+      </c>
+      <c r="O65" s="18">
+        <f t="shared" ref="O65:O66" si="34">SUM(C65:N65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C58" s="20">
-        <v>0</v>
-      </c>
-      <c r="D58" s="20">
-        <v>0</v>
-      </c>
-      <c r="E58" s="20">
-        <v>0</v>
-      </c>
-      <c r="F58" s="20">
-        <v>0</v>
-      </c>
-      <c r="G58" s="20">
-        <v>0</v>
-      </c>
-      <c r="H58" s="20">
-        <v>0</v>
-      </c>
-      <c r="I58" s="20">
-        <v>0</v>
-      </c>
-      <c r="J58" s="20">
-        <v>0</v>
-      </c>
-      <c r="K58" s="20">
-        <v>0</v>
-      </c>
-      <c r="L58" s="20">
-        <v>0</v>
-      </c>
-      <c r="M58" s="20">
-        <v>0</v>
-      </c>
-      <c r="N58" s="20">
-        <v>0</v>
-      </c>
-      <c r="O58" s="18">
-        <f t="shared" ref="O58:O59" si="11">SUM(C58:N58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B59" s="19" t="s">
+      <c r="C66" s="20">
+        <v>0</v>
+      </c>
+      <c r="D66" s="20">
+        <v>0</v>
+      </c>
+      <c r="E66" s="20">
+        <v>0</v>
+      </c>
+      <c r="F66" s="20">
+        <v>0</v>
+      </c>
+      <c r="G66" s="20">
+        <v>0</v>
+      </c>
+      <c r="H66" s="20">
+        <v>0</v>
+      </c>
+      <c r="I66" s="20">
+        <v>0</v>
+      </c>
+      <c r="J66" s="20">
+        <v>0</v>
+      </c>
+      <c r="K66" s="20">
+        <v>0</v>
+      </c>
+      <c r="L66" s="20">
+        <v>0</v>
+      </c>
+      <c r="M66" s="20">
+        <v>0</v>
+      </c>
+      <c r="N66" s="20">
+        <v>0</v>
+      </c>
+      <c r="O66" s="18">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C59" s="20">
-        <v>0</v>
-      </c>
-      <c r="D59" s="20">
-        <v>0</v>
-      </c>
-      <c r="E59" s="20">
-        <v>0</v>
-      </c>
-      <c r="F59" s="20">
-        <v>0</v>
-      </c>
-      <c r="G59" s="20">
-        <v>0</v>
-      </c>
-      <c r="H59" s="20">
-        <v>0</v>
-      </c>
-      <c r="I59" s="20">
-        <v>0</v>
-      </c>
-      <c r="J59" s="20">
-        <v>0</v>
-      </c>
-      <c r="K59" s="20">
-        <v>0</v>
-      </c>
-      <c r="L59" s="20">
-        <v>0</v>
-      </c>
-      <c r="M59" s="20">
-        <v>0</v>
-      </c>
-      <c r="N59" s="20">
-        <v>0</v>
-      </c>
-      <c r="O59" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B60" s="19" t="s">
+      <c r="C67" s="20">
+        <v>0</v>
+      </c>
+      <c r="D67" s="20">
+        <v>0</v>
+      </c>
+      <c r="E67" s="20">
+        <v>0</v>
+      </c>
+      <c r="F67" s="20">
+        <v>0</v>
+      </c>
+      <c r="G67" s="20">
+        <v>0</v>
+      </c>
+      <c r="H67" s="20">
+        <v>0</v>
+      </c>
+      <c r="I67" s="20">
+        <v>0</v>
+      </c>
+      <c r="J67" s="20">
+        <v>0</v>
+      </c>
+      <c r="K67" s="20">
+        <v>0</v>
+      </c>
+      <c r="L67" s="20">
+        <v>0</v>
+      </c>
+      <c r="M67" s="20">
+        <v>0</v>
+      </c>
+      <c r="N67" s="20">
+        <v>0</v>
+      </c>
+      <c r="O67" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="20">
-        <v>0</v>
-      </c>
-      <c r="D60" s="20">
-        <v>0</v>
-      </c>
-      <c r="E60" s="20">
-        <v>0</v>
-      </c>
-      <c r="F60" s="20">
-        <v>0</v>
-      </c>
-      <c r="G60" s="20">
-        <v>0</v>
-      </c>
-      <c r="H60" s="20">
-        <v>0</v>
-      </c>
-      <c r="I60" s="20">
-        <v>0</v>
-      </c>
-      <c r="J60" s="20">
-        <v>0</v>
-      </c>
-      <c r="K60" s="20">
-        <v>0</v>
-      </c>
-      <c r="L60" s="20">
-        <v>0</v>
-      </c>
-      <c r="M60" s="20">
-        <v>0</v>
-      </c>
-      <c r="N60" s="20">
-        <v>0</v>
-      </c>
-      <c r="O60" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B61" s="19" t="s">
+      <c r="C68" s="20">
+        <v>0</v>
+      </c>
+      <c r="D68" s="20">
+        <v>0</v>
+      </c>
+      <c r="E68" s="20">
+        <v>0</v>
+      </c>
+      <c r="F68" s="20">
+        <v>0</v>
+      </c>
+      <c r="G68" s="20">
+        <v>0</v>
+      </c>
+      <c r="H68" s="20">
+        <v>0</v>
+      </c>
+      <c r="I68" s="20">
+        <v>0</v>
+      </c>
+      <c r="J68" s="20">
+        <v>0</v>
+      </c>
+      <c r="K68" s="20">
+        <v>0</v>
+      </c>
+      <c r="L68" s="20">
+        <v>0</v>
+      </c>
+      <c r="M68" s="20">
+        <v>0</v>
+      </c>
+      <c r="N68" s="20">
+        <v>0</v>
+      </c>
+      <c r="O68" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="45"/>
+      <c r="C69" s="20">
+        <v>0</v>
+      </c>
+      <c r="D69" s="20">
+        <v>0</v>
+      </c>
+      <c r="E69" s="20">
+        <v>0</v>
+      </c>
+      <c r="F69" s="20">
+        <v>0</v>
+      </c>
+      <c r="G69" s="20">
+        <v>0</v>
+      </c>
+      <c r="H69" s="20">
+        <v>0</v>
+      </c>
+      <c r="I69" s="20">
+        <v>0</v>
+      </c>
+      <c r="J69" s="20">
+        <v>0</v>
+      </c>
+      <c r="K69" s="20">
+        <v>0</v>
+      </c>
+      <c r="L69" s="20">
+        <v>0</v>
+      </c>
+      <c r="M69" s="20">
+        <v>0</v>
+      </c>
+      <c r="N69" s="20">
+        <v>0</v>
+      </c>
+      <c r="O69" s="18">
+        <f t="shared" ref="O69" si="35">SUM(C69:N69)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C70" s="44">
+        <f>SUM(C63:C69)</f>
+        <v>0</v>
+      </c>
+      <c r="D70" s="44">
+        <f t="shared" ref="D70:O70" si="36">SUM(D63:D69)</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="N70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="O70" s="44">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C61" s="20">
-        <v>0</v>
-      </c>
-      <c r="D61" s="20">
-        <v>0</v>
-      </c>
-      <c r="E61" s="20">
-        <v>0</v>
-      </c>
-      <c r="F61" s="20">
-        <v>0</v>
-      </c>
-      <c r="G61" s="20">
-        <v>0</v>
-      </c>
-      <c r="H61" s="20">
-        <v>0</v>
-      </c>
-      <c r="I61" s="20">
-        <v>0</v>
-      </c>
-      <c r="J61" s="20">
-        <v>0</v>
-      </c>
-      <c r="K61" s="20">
-        <v>0</v>
-      </c>
-      <c r="L61" s="20">
-        <v>0</v>
-      </c>
-      <c r="M61" s="20">
-        <v>0</v>
-      </c>
-      <c r="N61" s="20">
-        <v>0</v>
-      </c>
-      <c r="O61" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B62" s="19"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="20"/>
-      <c r="O62" s="18"/>
-    </row>
-    <row r="63" spans="2:15" s="37" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B63" s="16" t="s">
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="34"/>
+      <c r="K71" s="34"/>
+      <c r="L71" s="34"/>
+      <c r="M71" s="34"/>
+      <c r="N71" s="29"/>
+      <c r="O71" s="21"/>
+    </row>
+    <row r="72" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="36"/>
-      <c r="G63" s="36"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="36"/>
-      <c r="J63" s="36"/>
-      <c r="K63" s="36"/>
-      <c r="L63" s="36"/>
-      <c r="M63" s="36"/>
-      <c r="N63" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O63" s="21">
-        <f>SUM(O64:O71)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B64" s="19" t="s">
+      <c r="C72" s="20">
+        <v>0</v>
+      </c>
+      <c r="D72" s="20">
+        <v>0</v>
+      </c>
+      <c r="E72" s="20">
+        <v>0</v>
+      </c>
+      <c r="F72" s="20">
+        <v>0</v>
+      </c>
+      <c r="G72" s="20">
+        <v>0</v>
+      </c>
+      <c r="H72" s="20">
+        <v>0</v>
+      </c>
+      <c r="I72" s="20">
+        <v>0</v>
+      </c>
+      <c r="J72" s="20">
+        <v>0</v>
+      </c>
+      <c r="K72" s="20">
+        <v>0</v>
+      </c>
+      <c r="L72" s="20">
+        <v>0</v>
+      </c>
+      <c r="M72" s="20">
+        <v>0</v>
+      </c>
+      <c r="N72" s="20">
+        <v>0</v>
+      </c>
+      <c r="O72" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="20">
-        <v>0</v>
-      </c>
-      <c r="D64" s="20">
-        <v>0</v>
-      </c>
-      <c r="E64" s="20">
-        <v>0</v>
-      </c>
-      <c r="F64" s="20">
-        <v>0</v>
-      </c>
-      <c r="G64" s="20">
-        <v>0</v>
-      </c>
-      <c r="H64" s="20">
-        <v>0</v>
-      </c>
-      <c r="I64" s="20">
-        <v>0</v>
-      </c>
-      <c r="J64" s="20">
-        <v>0</v>
-      </c>
-      <c r="K64" s="20">
-        <v>0</v>
-      </c>
-      <c r="L64" s="20">
-        <v>0</v>
-      </c>
-      <c r="M64" s="20">
-        <v>0</v>
-      </c>
-      <c r="N64" s="20">
-        <v>0</v>
-      </c>
-      <c r="O64" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B65" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" s="20">
-        <v>0</v>
-      </c>
-      <c r="D65" s="20">
-        <v>0</v>
-      </c>
-      <c r="E65" s="20">
-        <v>0</v>
-      </c>
-      <c r="F65" s="20">
-        <v>0</v>
-      </c>
-      <c r="G65" s="20">
-        <v>0</v>
-      </c>
-      <c r="H65" s="20">
-        <v>0</v>
-      </c>
-      <c r="I65" s="20">
-        <v>0</v>
-      </c>
-      <c r="J65" s="20">
-        <v>0</v>
-      </c>
-      <c r="K65" s="20">
-        <v>0</v>
-      </c>
-      <c r="L65" s="20">
-        <v>0</v>
-      </c>
-      <c r="M65" s="20">
-        <v>0</v>
-      </c>
-      <c r="N65" s="20">
-        <v>0</v>
-      </c>
-      <c r="O65" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B66" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="20">
-        <v>0</v>
-      </c>
-      <c r="D66" s="20">
-        <v>0</v>
-      </c>
-      <c r="E66" s="20">
-        <v>0</v>
-      </c>
-      <c r="F66" s="20">
-        <v>0</v>
-      </c>
-      <c r="G66" s="20">
-        <v>0</v>
-      </c>
-      <c r="H66" s="20">
-        <v>0</v>
-      </c>
-      <c r="I66" s="20">
-        <v>0</v>
-      </c>
-      <c r="J66" s="20">
-        <v>0</v>
-      </c>
-      <c r="K66" s="20">
-        <v>0</v>
-      </c>
-      <c r="L66" s="20">
-        <v>0</v>
-      </c>
-      <c r="M66" s="20">
-        <v>0</v>
-      </c>
-      <c r="N66" s="20">
-        <v>0</v>
-      </c>
-      <c r="O66" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B67" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="20">
-        <v>0</v>
-      </c>
-      <c r="D67" s="20">
-        <v>0</v>
-      </c>
-      <c r="E67" s="20">
-        <v>0</v>
-      </c>
-      <c r="F67" s="20">
-        <v>0</v>
-      </c>
-      <c r="G67" s="20">
-        <v>0</v>
-      </c>
-      <c r="H67" s="20">
-        <v>0</v>
-      </c>
-      <c r="I67" s="20">
-        <v>0</v>
-      </c>
-      <c r="J67" s="20">
-        <v>0</v>
-      </c>
-      <c r="K67" s="20">
-        <v>0</v>
-      </c>
-      <c r="L67" s="20">
-        <v>0</v>
-      </c>
-      <c r="M67" s="20">
-        <v>0</v>
-      </c>
-      <c r="N67" s="20">
-        <v>0</v>
-      </c>
-      <c r="O67" s="18">
-        <f t="shared" ref="O67:O70" si="12">SUM(C67:N67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B68" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C68" s="20">
-        <v>0</v>
-      </c>
-      <c r="D68" s="20">
-        <v>0</v>
-      </c>
-      <c r="E68" s="20">
-        <v>0</v>
-      </c>
-      <c r="F68" s="20">
-        <v>0</v>
-      </c>
-      <c r="G68" s="20">
-        <v>0</v>
-      </c>
-      <c r="H68" s="20">
-        <v>0</v>
-      </c>
-      <c r="I68" s="20">
-        <v>0</v>
-      </c>
-      <c r="J68" s="20">
-        <v>0</v>
-      </c>
-      <c r="K68" s="20">
-        <v>0</v>
-      </c>
-      <c r="L68" s="20">
-        <v>0</v>
-      </c>
-      <c r="M68" s="20">
-        <v>0</v>
-      </c>
-      <c r="N68" s="20">
-        <v>0</v>
-      </c>
-      <c r="O68" s="18">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B69" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C69" s="20">
-        <v>0</v>
-      </c>
-      <c r="D69" s="20">
-        <v>0</v>
-      </c>
-      <c r="E69" s="20">
-        <v>0</v>
-      </c>
-      <c r="F69" s="20">
-        <v>0</v>
-      </c>
-      <c r="G69" s="20">
-        <v>0</v>
-      </c>
-      <c r="H69" s="20">
-        <v>0</v>
-      </c>
-      <c r="I69" s="20">
-        <v>0</v>
-      </c>
-      <c r="J69" s="20">
-        <v>0</v>
-      </c>
-      <c r="K69" s="20">
-        <v>0</v>
-      </c>
-      <c r="L69" s="20">
-        <v>0</v>
-      </c>
-      <c r="M69" s="20">
-        <v>0</v>
-      </c>
-      <c r="N69" s="20">
-        <v>0</v>
-      </c>
-      <c r="O69" s="18">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B70" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="20">
-        <v>0</v>
-      </c>
-      <c r="D70" s="20">
-        <v>0</v>
-      </c>
-      <c r="E70" s="20">
-        <v>0</v>
-      </c>
-      <c r="F70" s="20">
-        <v>0</v>
-      </c>
-      <c r="G70" s="20">
-        <v>0</v>
-      </c>
-      <c r="H70" s="20">
-        <v>0</v>
-      </c>
-      <c r="I70" s="20">
-        <v>0</v>
-      </c>
-      <c r="J70" s="20">
-        <v>0</v>
-      </c>
-      <c r="K70" s="20">
-        <v>0</v>
-      </c>
-      <c r="L70" s="20">
-        <v>0</v>
-      </c>
-      <c r="M70" s="20">
-        <v>0</v>
-      </c>
-      <c r="N70" s="20">
-        <v>0</v>
-      </c>
-      <c r="O70" s="18">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B71" s="19"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20"/>
-      <c r="K71" s="20"/>
-      <c r="L71" s="20"/>
-      <c r="M71" s="20"/>
-      <c r="N71" s="20"/>
-      <c r="O71" s="18"/>
-    </row>
-    <row r="72" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B72" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="J72" s="35"/>
-      <c r="K72" s="35"/>
-      <c r="L72" s="35"/>
-      <c r="M72" s="35"/>
-      <c r="N72" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O72" s="21">
-        <f>SUM(O73:O77)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B73" s="19" t="s">
-        <v>75</v>
-      </c>
       <c r="C73" s="20">
         <v>0</v>
       </c>
@@ -4816,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="18">
-        <f t="shared" ref="O73" si="13">SUM(C73:N73)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P73" s="15"/>
@@ -4922,9 +5301,9 @@
       <c r="DL73" s="15"/>
       <c r="DM73" s="15"/>
     </row>
-    <row r="74" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="74" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="19" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C74" s="20">
         <v>0</v>
@@ -4963,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="18">
-        <f t="shared" ref="O74:O82" si="14">SUM(C74:N74)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P74" s="15"/>
@@ -5069,9 +5448,9 @@
       <c r="DL74" s="15"/>
       <c r="DM74" s="15"/>
     </row>
-    <row r="75" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="75" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="19" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C75" s="20">
         <v>0</v>
@@ -5110,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="O75" s="18">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="O75:O78" si="37">SUM(C75:N75)</f>
         <v>0</v>
       </c>
       <c r="P75" s="15"/>
@@ -5216,9 +5595,9 @@
       <c r="DL75" s="15"/>
       <c r="DM75" s="15"/>
     </row>
-    <row r="76" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="76" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="19" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C76" s="20">
         <v>0</v>
@@ -5257,7 +5636,7 @@
         <v>0</v>
       </c>
       <c r="O76" s="18">
-        <f t="shared" ref="O76" si="15">SUM(C76:N76)</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="P76" s="15"/>
@@ -5363,21 +5742,50 @@
       <c r="DL76" s="15"/>
       <c r="DM76" s="15"/>
     </row>
-    <row r="77" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B77" s="19"/>
-      <c r="C77" s="20"/>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
-      <c r="J77" s="20"/>
-      <c r="K77" s="20"/>
-      <c r="L77" s="20"/>
-      <c r="M77" s="20"/>
-      <c r="N77" s="20"/>
-      <c r="O77" s="18"/>
+    <row r="77" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C77" s="20">
+        <v>0</v>
+      </c>
+      <c r="D77" s="20">
+        <v>0</v>
+      </c>
+      <c r="E77" s="20">
+        <v>0</v>
+      </c>
+      <c r="F77" s="20">
+        <v>0</v>
+      </c>
+      <c r="G77" s="20">
+        <v>0</v>
+      </c>
+      <c r="H77" s="20">
+        <v>0</v>
+      </c>
+      <c r="I77" s="20">
+        <v>0</v>
+      </c>
+      <c r="J77" s="20">
+        <v>0</v>
+      </c>
+      <c r="K77" s="20">
+        <v>0</v>
+      </c>
+      <c r="L77" s="20">
+        <v>0</v>
+      </c>
+      <c r="M77" s="20">
+        <v>0</v>
+      </c>
+      <c r="N77" s="20">
+        <v>0</v>
+      </c>
+      <c r="O77" s="18">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="P77" s="15"/>
       <c r="Q77" s="15"/>
       <c r="R77" s="15"/>
@@ -5481,26 +5889,48 @@
       <c r="DL77" s="15"/>
       <c r="DM77" s="15"/>
     </row>
-    <row r="78" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B78" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
-      <c r="J78" s="36"/>
-      <c r="K78" s="36"/>
-      <c r="L78" s="36"/>
-      <c r="M78" s="36"/>
-      <c r="N78" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O78" s="21">
-        <f>SUM(O79:O82)</f>
+    <row r="78" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C78" s="20">
+        <v>0</v>
+      </c>
+      <c r="D78" s="20">
+        <v>0</v>
+      </c>
+      <c r="E78" s="20">
+        <v>0</v>
+      </c>
+      <c r="F78" s="20">
+        <v>0</v>
+      </c>
+      <c r="G78" s="20">
+        <v>0</v>
+      </c>
+      <c r="H78" s="20">
+        <v>0</v>
+      </c>
+      <c r="I78" s="20">
+        <v>0</v>
+      </c>
+      <c r="J78" s="20">
+        <v>0</v>
+      </c>
+      <c r="K78" s="20">
+        <v>0</v>
+      </c>
+      <c r="L78" s="20">
+        <v>0</v>
+      </c>
+      <c r="M78" s="20">
+        <v>0</v>
+      </c>
+      <c r="N78" s="20">
+        <v>0</v>
+      </c>
+      <c r="O78" s="18">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="P78" s="15"/>
@@ -5606,10 +6036,8 @@
       <c r="DL78" s="15"/>
       <c r="DM78" s="15"/>
     </row>
-    <row r="79" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B79" s="19" t="s">
-        <v>80</v>
-      </c>
+    <row r="79" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="45"/>
       <c r="C79" s="20">
         <v>0</v>
       </c>
@@ -5647,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="18">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="O79" si="38">SUM(C79:N79)</f>
         <v>0</v>
       </c>
       <c r="P79" s="15"/>
@@ -5753,48 +6181,60 @@
       <c r="DL79" s="15"/>
       <c r="DM79" s="15"/>
     </row>
-    <row r="80" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B80" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" s="20">
-        <v>0</v>
-      </c>
-      <c r="D80" s="20">
-        <v>0</v>
-      </c>
-      <c r="E80" s="20">
-        <v>0</v>
-      </c>
-      <c r="F80" s="20">
-        <v>0</v>
-      </c>
-      <c r="G80" s="20">
-        <v>0</v>
-      </c>
-      <c r="H80" s="20">
-        <v>0</v>
-      </c>
-      <c r="I80" s="20">
-        <v>0</v>
-      </c>
-      <c r="J80" s="20">
-        <v>0</v>
-      </c>
-      <c r="K80" s="20">
-        <v>0</v>
-      </c>
-      <c r="L80" s="20">
-        <v>0</v>
-      </c>
-      <c r="M80" s="20">
-        <v>0</v>
-      </c>
-      <c r="N80" s="20">
-        <v>0</v>
-      </c>
-      <c r="O80" s="18">
-        <f t="shared" si="14"/>
+    <row r="80" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C80" s="44">
+        <f>SUM(C72:C79)</f>
+        <v>0</v>
+      </c>
+      <c r="D80" s="44">
+        <f t="shared" ref="D80:O80" si="39">SUM(D72:D79)</f>
+        <v>0</v>
+      </c>
+      <c r="E80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="G80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="J80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="L80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="M80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="N80" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O80" s="44">
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="P80" s="15"/>
@@ -5900,50 +6340,23 @@
       <c r="DL80" s="15"/>
       <c r="DM80" s="15"/>
     </row>
-    <row r="81" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B81" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" s="20">
-        <v>0</v>
-      </c>
-      <c r="D81" s="20">
-        <v>0</v>
-      </c>
-      <c r="E81" s="20">
-        <v>0</v>
-      </c>
-      <c r="F81" s="20">
-        <v>0</v>
-      </c>
-      <c r="G81" s="20">
-        <v>0</v>
-      </c>
-      <c r="H81" s="20">
-        <v>0</v>
-      </c>
-      <c r="I81" s="20">
-        <v>0</v>
-      </c>
-      <c r="J81" s="20">
-        <v>0</v>
-      </c>
-      <c r="K81" s="20">
-        <v>0</v>
-      </c>
-      <c r="L81" s="20">
-        <v>0</v>
-      </c>
-      <c r="M81" s="20">
-        <v>0</v>
-      </c>
-      <c r="N81" s="20">
-        <v>0</v>
-      </c>
-      <c r="O81" s="18">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
+    <row r="81" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" s="33"/>
+      <c r="D81" s="33"/>
+      <c r="E81" s="33"/>
+      <c r="F81" s="33"/>
+      <c r="G81" s="33"/>
+      <c r="H81" s="33"/>
+      <c r="I81" s="33"/>
+      <c r="J81" s="33"/>
+      <c r="K81" s="33"/>
+      <c r="L81" s="33"/>
+      <c r="M81" s="33"/>
+      <c r="N81" s="29"/>
+      <c r="O81" s="21"/>
       <c r="P81" s="15"/>
       <c r="Q81" s="15"/>
       <c r="R81" s="15"/>
@@ -6047,9 +6460,9 @@
       <c r="DL81" s="15"/>
       <c r="DM81" s="15"/>
     </row>
-    <row r="82" spans="2:117" s="34" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="82" spans="2:117" s="32" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="19" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C82" s="20">
         <v>0</v>
@@ -6088,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="18">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="O82" si="40">SUM(C82:N82)</f>
         <v>0</v>
       </c>
       <c r="P82" s="15"/>
@@ -6194,82 +6607,599 @@
       <c r="DL82" s="15"/>
       <c r="DM82" s="15"/>
     </row>
-    <row r="83" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B83" s="19"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-      <c r="J83" s="20"/>
-      <c r="K83" s="20"/>
-      <c r="L83" s="20"/>
-      <c r="M83" s="20"/>
-      <c r="N83" s="20"/>
-      <c r="O83" s="18"/>
-    </row>
-    <row r="84" spans="2:117" s="15" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B84" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C84" s="10">
-        <f>SUM(C28:C83)</f>
-        <v>0</v>
-      </c>
-      <c r="D84" s="10">
-        <f>SUM(D28:D83)</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="10">
-        <f>SUM(E28:E83)</f>
-        <v>0</v>
-      </c>
-      <c r="F84" s="10">
-        <f>SUM(F28:F83)</f>
-        <v>0</v>
-      </c>
-      <c r="G84" s="10">
-        <f>SUM(G28:G83)</f>
-        <v>0</v>
-      </c>
-      <c r="H84" s="10">
-        <f>SUM(H28:H83)</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="10">
-        <f>SUM(I28:I83)</f>
-        <v>0</v>
-      </c>
-      <c r="J84" s="10">
-        <f>SUM(J28:J83)</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="10">
-        <f>SUM(K28:K83)</f>
-        <v>0</v>
-      </c>
-      <c r="L84" s="10">
-        <f>SUM(L28:L83)</f>
-        <v>0</v>
-      </c>
-      <c r="M84" s="10">
-        <f>SUM(M28:M83)</f>
-        <v>0</v>
-      </c>
-      <c r="N84" s="10">
-        <f>SUM(N28:N83)</f>
-        <v>0</v>
-      </c>
-      <c r="O84" s="38">
+    <row r="83" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C83" s="20">
+        <v>0</v>
+      </c>
+      <c r="D83" s="20">
+        <v>0</v>
+      </c>
+      <c r="E83" s="20">
+        <v>0</v>
+      </c>
+      <c r="F83" s="20">
+        <v>0</v>
+      </c>
+      <c r="G83" s="20">
+        <v>0</v>
+      </c>
+      <c r="H83" s="20">
+        <v>0</v>
+      </c>
+      <c r="I83" s="20">
+        <v>0</v>
+      </c>
+      <c r="J83" s="20">
+        <v>0</v>
+      </c>
+      <c r="K83" s="20">
+        <v>0</v>
+      </c>
+      <c r="L83" s="20">
+        <v>0</v>
+      </c>
+      <c r="M83" s="20">
+        <v>0</v>
+      </c>
+      <c r="N83" s="20">
+        <v>0</v>
+      </c>
+      <c r="O83" s="18">
+        <f t="shared" ref="O83:O92" si="41">SUM(C83:N83)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:117" s="15" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C84" s="20">
+        <v>0</v>
+      </c>
+      <c r="D84" s="20">
+        <v>0</v>
+      </c>
+      <c r="E84" s="20">
+        <v>0</v>
+      </c>
+      <c r="F84" s="20">
+        <v>0</v>
+      </c>
+      <c r="G84" s="20">
+        <v>0</v>
+      </c>
+      <c r="H84" s="20">
+        <v>0</v>
+      </c>
+      <c r="I84" s="20">
+        <v>0</v>
+      </c>
+      <c r="J84" s="20">
+        <v>0</v>
+      </c>
+      <c r="K84" s="20">
+        <v>0</v>
+      </c>
+      <c r="L84" s="20">
+        <v>0</v>
+      </c>
+      <c r="M84" s="20">
+        <v>0</v>
+      </c>
+      <c r="N84" s="20">
+        <v>0</v>
+      </c>
+      <c r="O84" s="18">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:117" x14ac:dyDescent="0.2">
+      <c r="B85" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C85" s="20">
+        <v>0</v>
+      </c>
+      <c r="D85" s="20">
+        <v>0</v>
+      </c>
+      <c r="E85" s="20">
+        <v>0</v>
+      </c>
+      <c r="F85" s="20">
+        <v>0</v>
+      </c>
+      <c r="G85" s="20">
+        <v>0</v>
+      </c>
+      <c r="H85" s="20">
+        <v>0</v>
+      </c>
+      <c r="I85" s="20">
+        <v>0</v>
+      </c>
+      <c r="J85" s="20">
+        <v>0</v>
+      </c>
+      <c r="K85" s="20">
+        <v>0</v>
+      </c>
+      <c r="L85" s="20">
+        <v>0</v>
+      </c>
+      <c r="M85" s="20">
+        <v>0</v>
+      </c>
+      <c r="N85" s="20">
+        <v>0</v>
+      </c>
+      <c r="O85" s="18">
+        <f t="shared" ref="O85" si="42">SUM(C85:N85)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:117" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="45"/>
+      <c r="C86" s="20">
+        <v>0</v>
+      </c>
+      <c r="D86" s="20">
+        <v>0</v>
+      </c>
+      <c r="E86" s="20">
+        <v>0</v>
+      </c>
+      <c r="F86" s="20">
+        <v>0</v>
+      </c>
+      <c r="G86" s="20">
+        <v>0</v>
+      </c>
+      <c r="H86" s="20">
+        <v>0</v>
+      </c>
+      <c r="I86" s="20">
+        <v>0</v>
+      </c>
+      <c r="J86" s="20">
+        <v>0</v>
+      </c>
+      <c r="K86" s="20">
+        <v>0</v>
+      </c>
+      <c r="L86" s="20">
+        <v>0</v>
+      </c>
+      <c r="M86" s="20">
+        <v>0</v>
+      </c>
+      <c r="N86" s="20">
+        <v>0</v>
+      </c>
+      <c r="O86" s="18">
+        <f t="shared" ref="O86" si="43">SUM(C86:N86)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:117" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" s="44">
+        <f>SUM(C82:C86)</f>
+        <v>0</v>
+      </c>
+      <c r="D87" s="44">
+        <f t="shared" ref="D87:O87" si="44">SUM(D82:D86)</f>
+        <v>0</v>
+      </c>
+      <c r="E87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="H87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="J87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="K87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O87" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:117" x14ac:dyDescent="0.2">
+      <c r="B88" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C88" s="34"/>
+      <c r="D88" s="34"/>
+      <c r="E88" s="34"/>
+      <c r="F88" s="34"/>
+      <c r="G88" s="34"/>
+      <c r="H88" s="34"/>
+      <c r="I88" s="34"/>
+      <c r="J88" s="34"/>
+      <c r="K88" s="34"/>
+      <c r="L88" s="34"/>
+      <c r="M88" s="34"/>
+      <c r="N88" s="29"/>
+      <c r="O88" s="21"/>
+    </row>
+    <row r="89" spans="2:117" x14ac:dyDescent="0.2">
+      <c r="B89" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C89" s="20">
+        <v>0</v>
+      </c>
+      <c r="D89" s="20">
+        <v>0</v>
+      </c>
+      <c r="E89" s="20">
+        <v>0</v>
+      </c>
+      <c r="F89" s="20">
+        <v>0</v>
+      </c>
+      <c r="G89" s="20">
+        <v>0</v>
+      </c>
+      <c r="H89" s="20">
+        <v>0</v>
+      </c>
+      <c r="I89" s="20">
+        <v>0</v>
+      </c>
+      <c r="J89" s="20">
+        <v>0</v>
+      </c>
+      <c r="K89" s="20">
+        <v>0</v>
+      </c>
+      <c r="L89" s="20">
+        <v>0</v>
+      </c>
+      <c r="M89" s="20">
+        <v>0</v>
+      </c>
+      <c r="N89" s="20">
+        <v>0</v>
+      </c>
+      <c r="O89" s="18">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:117" x14ac:dyDescent="0.2">
+      <c r="B90" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C90" s="20">
+        <v>0</v>
+      </c>
+      <c r="D90" s="20">
+        <v>0</v>
+      </c>
+      <c r="E90" s="20">
+        <v>0</v>
+      </c>
+      <c r="F90" s="20">
+        <v>0</v>
+      </c>
+      <c r="G90" s="20">
+        <v>0</v>
+      </c>
+      <c r="H90" s="20">
+        <v>0</v>
+      </c>
+      <c r="I90" s="20">
+        <v>0</v>
+      </c>
+      <c r="J90" s="20">
+        <v>0</v>
+      </c>
+      <c r="K90" s="20">
+        <v>0</v>
+      </c>
+      <c r="L90" s="20">
+        <v>0</v>
+      </c>
+      <c r="M90" s="20">
+        <v>0</v>
+      </c>
+      <c r="N90" s="20">
+        <v>0</v>
+      </c>
+      <c r="O90" s="18">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:117" x14ac:dyDescent="0.2">
+      <c r="B91" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" s="20">
+        <v>0</v>
+      </c>
+      <c r="D91" s="20">
+        <v>0</v>
+      </c>
+      <c r="E91" s="20">
+        <v>0</v>
+      </c>
+      <c r="F91" s="20">
+        <v>0</v>
+      </c>
+      <c r="G91" s="20">
+        <v>0</v>
+      </c>
+      <c r="H91" s="20">
+        <v>0</v>
+      </c>
+      <c r="I91" s="20">
+        <v>0</v>
+      </c>
+      <c r="J91" s="20">
+        <v>0</v>
+      </c>
+      <c r="K91" s="20">
+        <v>0</v>
+      </c>
+      <c r="L91" s="20">
+        <v>0</v>
+      </c>
+      <c r="M91" s="20">
+        <v>0</v>
+      </c>
+      <c r="N91" s="20">
+        <v>0</v>
+      </c>
+      <c r="O91" s="18">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:117" x14ac:dyDescent="0.2">
+      <c r="B92" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C92" s="20">
+        <v>0</v>
+      </c>
+      <c r="D92" s="20">
+        <v>0</v>
+      </c>
+      <c r="E92" s="20">
+        <v>0</v>
+      </c>
+      <c r="F92" s="20">
+        <v>0</v>
+      </c>
+      <c r="G92" s="20">
+        <v>0</v>
+      </c>
+      <c r="H92" s="20">
+        <v>0</v>
+      </c>
+      <c r="I92" s="20">
+        <v>0</v>
+      </c>
+      <c r="J92" s="20">
+        <v>0</v>
+      </c>
+      <c r="K92" s="20">
+        <v>0</v>
+      </c>
+      <c r="L92" s="20">
+        <v>0</v>
+      </c>
+      <c r="M92" s="20">
+        <v>0</v>
+      </c>
+      <c r="N92" s="20">
+        <v>0</v>
+      </c>
+      <c r="O92" s="18">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:117" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="45"/>
+      <c r="C93" s="20">
+        <v>0</v>
+      </c>
+      <c r="D93" s="20">
+        <v>0</v>
+      </c>
+      <c r="E93" s="20">
+        <v>0</v>
+      </c>
+      <c r="F93" s="20">
+        <v>0</v>
+      </c>
+      <c r="G93" s="20">
+        <v>0</v>
+      </c>
+      <c r="H93" s="20">
+        <v>0</v>
+      </c>
+      <c r="I93" s="20">
+        <v>0</v>
+      </c>
+      <c r="J93" s="20">
+        <v>0</v>
+      </c>
+      <c r="K93" s="20">
+        <v>0</v>
+      </c>
+      <c r="L93" s="20">
+        <v>0</v>
+      </c>
+      <c r="M93" s="20">
+        <v>0</v>
+      </c>
+      <c r="N93" s="20">
+        <v>0</v>
+      </c>
+      <c r="O93" s="18">
+        <f t="shared" ref="O93" si="45">SUM(C93:N93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:117" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C94" s="44">
+        <f>SUM(C89:C93)</f>
+        <v>0</v>
+      </c>
+      <c r="D94" s="44">
+        <f t="shared" ref="D94:O94" si="46">SUM(D89:D93)</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="H94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="I94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="K94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="L94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="N94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O94" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:117" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C95" s="10">
+        <f>SUM(C33:C43,C46:C52,C55:C60,C63:C69,C72:C79,C82:C86,C89:C93)</f>
+        <v>0</v>
+      </c>
+      <c r="D95" s="10">
+        <f t="shared" ref="D95:N95" si="47">SUM(D33:D43,D46:D52,D55:D60,D63:D69,D72:D79,D82:D86,D89:D93)</f>
+        <v>0</v>
+      </c>
+      <c r="E95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="G95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="H95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="I95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="J95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="K95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="L95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="M95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="N95" s="10">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="O95" s="36">
         <f>SUM(outcomes[[#This Row],[Janvier]:[Déc]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:117">
-      <c r="B90" s="25"/>
-      <c r="E90" s="2"/>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B101" s="25"/>
+      <c r="E101" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6292,9 +7222,21 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100668883340522464AA753139DE61DFBF4" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4184e77cb73992caa9a76c50e31ad1a5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a0aec67c-13da-4bd3-bf62-07b4602bf127" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89bb83f0351a06b8b6a2a97efaea3038" ns2:_="">
-    <xsd:import namespace="a0aec67c-13da-4bd3-bf62-07b4602bf127"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d0c3f830-cbab-496c-8f0c-6aa244f81dd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D8CC7E5D8C7F6B4E9C91972CAFAEB4E7" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b46d8005feeca84e0b112a99a0b8f397">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe" xmlns:ns3="d0c3f830-cbab-496c-8f0c-6aa244f81dd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="76ce2a396ed138893fb1228542f732a5" ns2:_="" ns3:_="">
+    <xsd:import namespace="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe"/>
+    <xsd:import namespace="d0c3f830-cbab-496c-8f0c-6aa244f81dd7"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -6304,6 +7246,14 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -6311,7 +7261,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a0aec67c-13da-4bd3-bf62-07b4602bf127" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -6328,6 +7278,60 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="33941350-b5ef-4818-a0e5-cb5605a3d307" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0c3f830-cbab-496c-8f0c-6aa244f81dd7" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{357b441e-d6c7-4404-a47c-0a66b3c72bc7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0c3f830-cbab-496c-8f0c-6aa244f81dd7">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -6429,20 +7433,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF5442E9-F47E-455A-9E32-A74D6623B3F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF5442E9-F47E-455A-9E32-A74D6623B3F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3F675B1-F4FE-4133-9BC0-FB32C00F47A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C8D831E-4A68-43BB-8A70-37E067820D34}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="d0c3f830-cbab-496c-8f0c-6aa244f81dd7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C8D831E-4A68-43BB-8A70-37E067820D34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08A187BB-FCFD-44C5-89F3-6869AD792AF1}"/>
 </file>